--- a/marketing_report/outputs/Grado_Pregrado/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,16 +464,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4591</v>
+        <v>11363</v>
       </c>
       <c r="C2" t="n">
-        <v>4591</v>
+        <v>3222</v>
       </c>
       <c r="D2" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="3">
@@ -483,54 +483,54 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4371</v>
+        <v>5861</v>
       </c>
       <c r="C3" t="n">
-        <v>4371</v>
+        <v>543</v>
       </c>
       <c r="D3" t="n">
-        <v>484</v>
+        <v>53</v>
       </c>
       <c r="E3" t="n">
-        <v>11.07</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14876203835</t>
+          <t>14875022827</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2804</v>
+        <v>4846</v>
       </c>
       <c r="C4" t="n">
-        <v>2804</v>
+        <v>1329</v>
       </c>
       <c r="D4" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>2.67</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14875022827</t>
+          <t>14876203835</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1923</v>
+        <v>4260</v>
       </c>
       <c r="C5" t="n">
-        <v>1923</v>
+        <v>506</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>1.14</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="6">
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1556</v>
+        <v>2621</v>
       </c>
       <c r="C6" t="n">
-        <v>1556</v>
+        <v>730</v>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>4.82</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="7">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>692</v>
+        <v>1504</v>
       </c>
       <c r="C7" t="n">
-        <v>692</v>
+        <v>387</v>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>3.32</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="8">
@@ -578,73 +578,73 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>663</v>
+        <v>1450</v>
       </c>
       <c r="C8" t="n">
-        <v>663</v>
+        <v>338</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14892349860</t>
+          <t>20612364611</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>545</v>
+        <v>1018</v>
       </c>
       <c r="C9" t="n">
-        <v>545</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15360035696</t>
+          <t>14909435507</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>469</v>
+        <v>975</v>
       </c>
       <c r="C10" t="n">
-        <v>469</v>
+        <v>263</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2.56</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21772187688</t>
+          <t>14892349860</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>441</v>
+        <v>914</v>
       </c>
       <c r="C11" t="n">
-        <v>441</v>
+        <v>198</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="12">
@@ -654,73 +654,73 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>430</v>
+        <v>903</v>
       </c>
       <c r="C12" t="n">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>2.79</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14909435507</t>
+          <t>19230946036</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>421</v>
+        <v>822</v>
       </c>
       <c r="C13" t="n">
-        <v>421</v>
+        <v>185</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.95</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19230946036</t>
+          <t>21772187688</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>384</v>
+        <v>706</v>
       </c>
       <c r="C14" t="n">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20612364611</t>
+          <t>15360035696</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>357</v>
+        <v>706</v>
       </c>
       <c r="C15" t="n">
-        <v>357</v>
+        <v>122</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.36</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="16">
@@ -730,92 +730,92 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>304</v>
+        <v>699</v>
       </c>
       <c r="C16" t="n">
-        <v>304</v>
+        <v>178</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>3.29</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14905247697</t>
+          <t>14899816755</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>296</v>
+        <v>635</v>
       </c>
       <c r="C17" t="n">
-        <v>296</v>
+        <v>179</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15357460006</t>
+          <t>14909223761</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>293</v>
+        <v>587</v>
       </c>
       <c r="C18" t="n">
-        <v>293</v>
+        <v>139</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>3.41</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14899816755</t>
+          <t>20721117289</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>283</v>
+        <v>581</v>
       </c>
       <c r="C19" t="n">
-        <v>283</v>
+        <v>134</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>1.77</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14891543883</t>
+          <t>15357460006</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>269</v>
+        <v>555</v>
       </c>
       <c r="C20" t="n">
-        <v>269</v>
+        <v>124</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>2.23</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="21">
@@ -825,35 +825,35 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>267</v>
+        <v>528</v>
       </c>
       <c r="C21" t="n">
-        <v>267</v>
+        <v>115</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>3.37</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14909223761</t>
+          <t>14905247697</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>266</v>
+        <v>517</v>
       </c>
       <c r="C22" t="n">
-        <v>266</v>
+        <v>121</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="23">
@@ -863,35 +863,35 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>266</v>
+        <v>490</v>
       </c>
       <c r="C23" t="n">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>3.38</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20721117289</t>
+          <t>14891543883</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>262</v>
+        <v>486</v>
       </c>
       <c r="C24" t="n">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>195</v>
+        <v>446</v>
       </c>
       <c r="C25" t="n">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.08</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14909096324</t>
+          <t>15767139553</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>174</v>
+        <v>412</v>
       </c>
       <c r="C26" t="n">
-        <v>174</v>
+        <v>112</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.75</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="27">
@@ -939,263 +939,263 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>174</v>
+        <v>404</v>
       </c>
       <c r="C27" t="n">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>15767139553</t>
+          <t>14896121927</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>168</v>
+        <v>356</v>
       </c>
       <c r="C28" t="n">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14896121927</t>
+          <t>14909096324</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>147</v>
+        <v>299</v>
       </c>
       <c r="C29" t="n">
-        <v>147</v>
+        <v>67</v>
       </c>
       <c r="D29" t="n">
         <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>2.72</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14894392756</t>
+          <t>14894109331</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>132</v>
+        <v>286</v>
       </c>
       <c r="C30" t="n">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="D30" t="n">
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>4.55</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15232856055</t>
+          <t>14894392756</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="C31" t="n">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.38</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14894109331</t>
+          <t>15232856055</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>129</v>
+        <v>243</v>
       </c>
       <c r="C32" t="n">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>11.63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>16552752228</t>
+          <t>22644502976</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>123</v>
+        <v>224</v>
       </c>
       <c r="C33" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>22644502976</t>
+          <t>16552752228</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="C34" t="n">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>23044564068</t>
+          <t>14905339848</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="C35" t="n">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>10.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14905339848</t>
+          <t>23078267428</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="C36" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>23277494379</t>
+          <t>8357919511</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="C37" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>23078267428</t>
+          <t>23044564068</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C38" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>7.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8357919511</t>
+          <t>14905619205</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="C39" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>1.85</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14905619205</t>
+          <t>23277494379</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C40" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1205,48 +1205,48 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C41" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>10.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15034800468</t>
+          <t>11749265729</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20531309410</t>
+          <t>22647879775</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1258,30 +1258,30 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21778508075</t>
+          <t>20998371077</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C44" t="n">
         <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>23041074431</t>
+          <t>22758675353</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C45" t="n">
         <v>3</v>
@@ -1296,11 +1296,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20523462698</t>
+          <t>20531309410</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
@@ -1315,14 +1315,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20917818431</t>
+          <t>15034800468</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15069068625</t>
+          <t>20523462698</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -1353,49 +1353,49 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15073321634</t>
+          <t>23041074431</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23255356694</t>
+          <t>21778508075</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15034827564</t>
+          <t>22637500317</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -1410,19 +1410,247 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>21933203642</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>21996147342</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>23255356694</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>15773753483</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>23040805580</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>22454462079</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20998490630</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20917818431</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>12018552619</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>15069068625</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>15034827564</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>14941637467</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>branding</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1437,7 +1665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1474,16 +1702,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23912</v>
+        <v>46675</v>
       </c>
       <c r="C2" t="n">
-        <v>23912</v>
+        <v>10649</v>
       </c>
       <c r="D2" t="n">
-        <v>956</v>
+        <v>327</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="3">
@@ -1493,15 +1721,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>121</v>
+        <v>228</v>
       </c>
       <c r="C3" t="n">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>brandingvideo</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1516,7 +1763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E291"/>
+  <dimension ref="A1:E378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,54 +1800,54 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1624</v>
+        <v>3004</v>
       </c>
       <c r="C2" t="n">
-        <v>1624</v>
+        <v>563</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>2.09</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>universidad catolica de salta</t>
+          <t>carreras universitarias</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1321</v>
+        <v>2200</v>
       </c>
       <c r="C3" t="n">
-        <v>1321</v>
+        <v>823</v>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>universidad virtual</t>
+          <t>universidad catolica de salta</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1171</v>
+        <v>2101</v>
       </c>
       <c r="C4" t="n">
-        <v>1171</v>
+        <v>267</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>2.48</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="5">
@@ -1610,73 +1857,73 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>643</v>
+        <v>1944</v>
       </c>
       <c r="C5" t="n">
-        <v>643</v>
+        <v>545</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.47</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>licenciatura en educacion fisica y deportes</t>
+          <t>universidad virtual</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>482</v>
+        <v>1667</v>
       </c>
       <c r="C6" t="n">
-        <v>482</v>
+        <v>310</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1.24</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>carreras universitarias a distancia</t>
+          <t>carrera de higiene y seguridad</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>450</v>
+        <v>790</v>
       </c>
       <c r="C7" t="n">
-        <v>450</v>
+        <v>175</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>2.44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>carreras universitarias</t>
+          <t>licenciatura en educacion fisica y deportes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>406</v>
+        <v>778</v>
       </c>
       <c r="C8" t="n">
-        <v>406</v>
+        <v>158</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="9">
@@ -1686,276 +1933,276 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>388</v>
+        <v>769</v>
       </c>
       <c r="C9" t="n">
-        <v>388</v>
+        <v>184</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>carrera de higiene y seguridad</t>
+          <t>carreras online</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>370</v>
+        <v>719</v>
       </c>
       <c r="C10" t="n">
-        <v>370</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2.16</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>universidad de criminologia</t>
+          <t>carreras universitarias a distancia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>368</v>
+        <v>715</v>
       </c>
       <c r="C11" t="n">
-        <v>368</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>formación profesional online</t>
+          <t>abogacia a distancia</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>360</v>
+        <v>566</v>
       </c>
       <c r="C12" t="n">
-        <v>360</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>1.11</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>carreras online</t>
+          <t>estudiar online</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>345</v>
+        <v>563</v>
       </c>
       <c r="C13" t="n">
-        <v>345</v>
+        <v>183</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>2.03</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>abogacia a distancia</t>
+          <t>universidad de criminologia</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>286</v>
+        <v>538</v>
       </c>
       <c r="C14" t="n">
-        <v>286</v>
+        <v>95</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>licenciatura en gestión educativa</t>
+          <t>licenciatura en seguridad</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>271</v>
+        <v>504</v>
       </c>
       <c r="C15" t="n">
-        <v>271</v>
+        <v>143</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>carreras cortas virtuales</t>
+          <t>estudiar contabilidad</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>264</v>
+        <v>484</v>
       </c>
       <c r="C16" t="n">
-        <v>264</v>
+        <v>117</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.52</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ciberseguridad carrera</t>
+          <t>universidad de salta</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>250</v>
+        <v>476</v>
       </c>
       <c r="C17" t="n">
-        <v>250</v>
+        <v>156</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>carreras virtuales</t>
+          <t>carreras cortas virtuales</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>247</v>
+        <v>476</v>
       </c>
       <c r="C18" t="n">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>estudiar gestion de calidad</t>
+          <t>universidad de quilmes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>229</v>
+        <v>473</v>
       </c>
       <c r="C19" t="n">
-        <v>229</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>licenciatura en seguridad</t>
+          <t>licenciatura en gestión educativa</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>220</v>
+        <v>464</v>
       </c>
       <c r="C20" t="n">
-        <v>220</v>
+        <v>104</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>0.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>estudiar contabilidad</t>
+          <t>estudiar gestion de calidad</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>208</v>
+        <v>463</v>
       </c>
       <c r="C21" t="n">
-        <v>208</v>
+        <v>125</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>estudiar comercio internacional</t>
+          <t>ciberseguridad carrera</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>195</v>
+        <v>459</v>
       </c>
       <c r="C22" t="n">
-        <v>195</v>
+        <v>96</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>1.54</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>universidad de quilmes</t>
+          <t>formación profesional online</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>161</v>
+        <v>418</v>
       </c>
       <c r="C23" t="n">
-        <v>161</v>
+        <v>54</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1967,20 +2214,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>estudiar a distancia en argentina</t>
+          <t>mineria en argentina</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>159</v>
+        <v>407</v>
       </c>
       <c r="C24" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.4</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="25">
@@ -1990,472 +2237,472 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>157</v>
+        <v>384</v>
       </c>
       <c r="C25" t="n">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>corredor inmobiliario carrera</t>
+          <t>estudiar comercio internacional</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>157</v>
+        <v>359</v>
       </c>
       <c r="C26" t="n">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>relaciones internacionales carrera</t>
+          <t>corredor inmobiliario carrera</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>156</v>
+        <v>354</v>
       </c>
       <c r="C27" t="n">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>6.41</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>recursos humanos</t>
+          <t>estudiar a distancia en argentina</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>154</v>
+        <v>351</v>
       </c>
       <c r="C28" t="n">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>1.95</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>carrera de derecho</t>
+          <t>carreras virtuales</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>148</v>
+        <v>350</v>
       </c>
       <c r="C29" t="n">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>administracion de empresas agropecuarias</t>
+          <t>recursos humanos</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>146</v>
+        <v>347</v>
       </c>
       <c r="C30" t="n">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>abogacia</t>
+          <t>carrera de derecho</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>133</v>
+        <v>328</v>
       </c>
       <c r="C31" t="n">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.26</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>estudios con salida laboral</t>
+          <t>universidad blas pascal</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>129</v>
+        <v>322</v>
       </c>
       <c r="C32" t="n">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>0.78</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ingeniería en minas</t>
+          <t>ucasal carreras a distancia</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>128</v>
+        <v>319</v>
       </c>
       <c r="C33" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>4.69</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>educación superior virtual</t>
+          <t>carreras cortas</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>124</v>
+        <v>309</v>
       </c>
       <c r="C34" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>licenciatura en entrenamiento deportivo</t>
+          <t>estudiar protocolo</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>123</v>
+        <v>288</v>
       </c>
       <c r="C35" t="n">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>estudiar protocolo</t>
+          <t>ucasal abogacia a distancia</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>123</v>
+        <v>279</v>
       </c>
       <c r="C36" t="n">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E36" t="n">
-        <v>2.44</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>carrera martillero publico a distancia</t>
+          <t>carreras a distancia</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>122</v>
+        <v>262</v>
       </c>
       <c r="C37" t="n">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>licenciatura en administracion de empresas</t>
+          <t>ingeniería en minas</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>121</v>
+        <v>261</v>
       </c>
       <c r="C38" t="n">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.31</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>universidad blas pascal</t>
+          <t>relaciones internacionales carrera</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="C39" t="n">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>administracion bancaria</t>
+          <t>administracion de empresas agropecuarias</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>118</v>
+        <v>258</v>
       </c>
       <c r="C40" t="n">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>estudiar agente inmobiliario</t>
+          <t>carrera martillero publico a distancia</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>116</v>
+        <v>255</v>
       </c>
       <c r="C41" t="n">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>universidad de salta</t>
+          <t>licenciatura en administracion de empresas</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>116</v>
+        <v>254</v>
       </c>
       <c r="C42" t="n">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="D42" t="n">
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.72</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ciencia de datos</t>
+          <t>estudiar agente inmobiliario</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>114</v>
+        <v>237</v>
       </c>
       <c r="C43" t="n">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.26</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>estudiar online</t>
+          <t>abogacia</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>102</v>
+        <v>229</v>
       </c>
       <c r="C44" t="n">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ucasal carreras a distancia</t>
+          <t>martillero corredor público y corredor inmobiliario</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>101</v>
+        <v>229</v>
       </c>
       <c r="C45" t="n">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>martillero corredor público y corredor inmobiliario</t>
+          <t>administracion bancaria</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>100</v>
+        <v>218</v>
       </c>
       <c r="C46" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cursos universitarios a distancia</t>
+          <t>ciencia de datos</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>96</v>
+        <v>213</v>
       </c>
       <c r="C47" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>5.21</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>mineria en argentina</t>
+          <t>universidad kennedy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>92</v>
+        <v>211</v>
       </c>
       <c r="C48" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>contador carrera</t>
+          <t>licenciatura en entrenamiento deportivo</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>84</v>
+        <v>211</v>
       </c>
       <c r="C49" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>3.57</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="50">
@@ -2465,10 +2712,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="C50" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2480,39 +2727,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>secretariado administrativo online</t>
+          <t>contador carrera</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="C51" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>carreras a distancia</t>
+          <t>universidad siglo 21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="C52" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2522,124 +2769,124 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="C53" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.53</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>que estudiar para ser agente inmobiliario</t>
+          <t>facultades online en argentina</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="C54" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>carrera universitaria</t>
+          <t>educación superior virtual</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="C55" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>universidad online</t>
+          <t>estudios con salida laboral</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="C56" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.48</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>recursos humanos carrera</t>
+          <t>siglo 21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="C57" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>1.37</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>carreras energias renovables</t>
+          <t>cursos universitarios a distancia</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="C58" t="n">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>1.41</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>universidad siglo 21</t>
+          <t>licenciatura de seguridad publica</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="C59" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2651,166 +2898,166 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ucasal abogacia a distancia</t>
+          <t>ucasal a distancia</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="C60" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>licenciatura de seguridad publica</t>
+          <t>secretariado administrativo online</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64</v>
+        <v>148</v>
       </c>
       <c r="C61" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>carrera de economia</t>
+          <t>universidades en jujuy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="C62" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.45</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>estudiar secretariado</t>
+          <t>recursos humanos carrera</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="C63" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>3.39</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>marketing digital carrera</t>
+          <t>estudiar martillero publico</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="C64" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="D64" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>13.56</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>carreras universitarias virtuales</t>
+          <t>que estudiar para ser agente inmobiliario</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="C65" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>facultades online en argentina</t>
+          <t>carrera de economia</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="C66" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.79</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>estudiar martillero publico</t>
+          <t>universidades en misiones</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="C67" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>estudiar criminología</t>
+          <t>estudiar secretariado</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="C68" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -2822,14 +3069,14 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>tecnicatura en seguros</t>
+          <t>carreras energias renovables</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="C69" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -2841,33 +3088,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>universidades en jujuy</t>
+          <t>tecnicatura en seguros</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="C70" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>2.04</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>carreras universitarias online</t>
+          <t>siglo 21 carreras</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="C71" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -2879,52 +3126,52 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>negocios digitales</t>
+          <t>universidad fasta</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="C72" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.13</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>carreras cortas</t>
+          <t>tec gestion de calidad</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="C73" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>siglo 21</t>
+          <t>estudiar a distancia</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="C74" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -2936,30 +3183,30 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>economia carrera</t>
+          <t>marketing digital carrera</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="C75" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.33</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>carrera en seguridad</t>
+          <t>universidad a distancia</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="C76" t="n">
         <v>40</v>
@@ -2974,33 +3221,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>licenciatura en lenguajes expresivos</t>
+          <t>comercio exterior carrera</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="C77" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>10.26</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>universidad kennedy</t>
+          <t>economia carrera</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="C78" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -3012,52 +3259,52 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>tecnicatura en ceremonial y protocolo</t>
+          <t>opciones para estudiar online</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="C79" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>estudios online universitarios</t>
+          <t>curso de banca y finanzas</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="C80" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ucasal a distancia</t>
+          <t>carrera para secretaria</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="C81" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -3069,33 +3316,33 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>criminología universidades</t>
+          <t>tecnicatura en ceremonial y protocolo</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="C82" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>8.109999999999999</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>estudiar y trabajar a la vez</t>
+          <t>carreras universitarias online</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="C83" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -3107,20 +3354,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comercio exterior carrera</t>
+          <t>negocios digitales</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3130,29 +3377,29 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C85" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>17.14</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tecnico agropecuario a distancia</t>
+          <t>estudiar criminología</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="C86" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3164,33 +3411,33 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>tec gestion de calidad</t>
+          <t>carrera universitaria</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="C87" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>universidad fasta</t>
+          <t>carrera en seguridad</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="C88" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -3202,20 +3449,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>opciones para estudiar online</t>
+          <t>universidad online</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="C89" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="90">
@@ -3225,29 +3472,29 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="C90" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>estudiar ciberseguridad</t>
+          <t>carreras universitarias virtuales</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="C91" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -3259,71 +3506,71 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>curso de banca y finanzas</t>
+          <t>escribania ucasal</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C92" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>siglo 21 carreras</t>
+          <t>técnico en mineria</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C93" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>licenciatura en administración agraria</t>
+          <t>educacion a distancia</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C94" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>estudiar a distancia</t>
+          <t>universidades en neuquen</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C95" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -3335,30 +3582,30 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>escribania ucasal</t>
+          <t>estudiar ciberseguridad</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="C96" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>universidad a distancia</t>
+          <t>carreras online argentina</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="C97" t="n">
         <v>26</v>
@@ -3373,33 +3620,33 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>modalidad virtual universitaria</t>
+          <t>licenciatura en lenguajes expresivos</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C98" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>educación superior a distancia</t>
+          <t>criminología universidades</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C99" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -3411,33 +3658,33 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>carrera de relaciones publicas</t>
+          <t>carrera de administracion</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C100" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>carrera para secretaria</t>
+          <t>tecnico agropecuario a distancia</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="C101" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -3449,33 +3696,33 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>carrera de protocolo</t>
+          <t>estudiar licenciatura</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C102" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>4.35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>técnico en mineria</t>
+          <t>estudiar mineria</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C103" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -3487,14 +3734,14 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>universidades en neuquen</t>
+          <t>licenciatura en administración agraria</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="C104" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -3506,14 +3753,14 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>estudiar mineria</t>
+          <t>universidades en salta</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C105" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -3525,14 +3772,14 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>carrera gestion educativa</t>
+          <t>estudios online universitarios</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C106" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -3544,33 +3791,33 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>carreras agropecuarias</t>
+          <t>licenciatura en recursos humanos</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C107" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>licenciatura en recursos humanos</t>
+          <t>estudiar y trabajar a la vez</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C108" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -3582,90 +3829,90 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>relaciones publicas carrera</t>
+          <t>educación superior a distancia</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C109" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>carrera de comercio exterior y aduanas</t>
+          <t>estudiar marketing</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C110" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>licenciatura en economia a distancia</t>
+          <t>licenciatura en actividad fisica y deporte</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C111" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>abogacia siglo 21</t>
+          <t>modalidad virtual universitaria</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C112" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>carreras agropecuarias a distancia</t>
+          <t>carrera productor de seguros</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C113" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -3677,14 +3924,14 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>licenciatura en actividad fisica y deporte</t>
+          <t>estudiar licenciatura en educacion fisica</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C114" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -3696,33 +3943,33 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>estudiar virtual</t>
+          <t>unsa</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C115" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>carrera de bancario</t>
+          <t>las carreras universitarias</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C116" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -3734,14 +3981,14 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>universidades online argentina</t>
+          <t>carreras bancarias</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C117" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -3753,14 +4000,14 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>las carreras universitarias</t>
+          <t>carreras agropecuarias a distancia</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C118" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -3772,52 +4019,52 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>estudiar marketing</t>
+          <t>licenciatura en economia a distancia</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C119" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D119" t="n">
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>6.25</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>mejores universidades online</t>
+          <t>relaciones publicas carrera</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C120" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>estudiar licenciatura en educacion fisica</t>
+          <t>carrera de protocolo</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C121" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -3829,14 +4076,14 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>estudiar licenciatura</t>
+          <t>carrera de relaciones publicas</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C122" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -3848,33 +4095,33 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>inscripciones de universidad</t>
+          <t>licenciatura en seguridad ciudadana</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C123" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>carreras con salida laboral online</t>
+          <t>carrera gestion educativa</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C124" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3886,14 +4133,14 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>carrera de administracion</t>
+          <t>universidad salta</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C125" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -3905,14 +4152,14 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>carreras bancarias</t>
+          <t>carreras a distancia argentina</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C126" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3924,14 +4171,14 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>tecnicatura en produccion agropecuaria</t>
+          <t>universidad a distancia argentina</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C127" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3943,14 +4190,14 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>universidades en misiones</t>
+          <t>licenciatura en administracion de empresas en linea</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C128" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3962,14 +4209,14 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>estudios carreras</t>
+          <t>abogacia siglo 21</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C129" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -3981,33 +4228,33 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>carrera productor de seguros</t>
+          <t>carrera de escribano</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C130" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D130" t="n">
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>7.14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>universidades a distancia oficiales</t>
+          <t>carreras agropecuarias</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C131" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -4019,14 +4266,14 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>licenciatura en seguridad ciudadana</t>
+          <t>escribanía distancia</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C132" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -4038,14 +4285,14 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>que carrera estudiar</t>
+          <t>protocolo y etiqueta en eventos</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C133" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -4057,33 +4304,33 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>facultades virtuales</t>
+          <t>carrera de comercio exterior y aduanas</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C134" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>universidades en salta</t>
+          <t>corredor inmobiliario a distancia</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C135" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -4095,14 +4342,14 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>comercio internacional y aduanas universidades</t>
+          <t>carrera gestion de calidad</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C136" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -4114,33 +4361,33 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>unsa</t>
+          <t>universidades online argentina</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C137" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>protocolo y etiqueta en eventos</t>
+          <t>carrera de bancario</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C138" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -4152,14 +4399,14 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>educación online</t>
+          <t>universidad de salta a distancia</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C139" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -4171,52 +4418,52 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>títulos universitarios online</t>
+          <t>carreras mineras para mujeres</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C140" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>licenciatura en ciencia de datos</t>
+          <t>tecnicatura en gestion de calidad</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C141" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>carrera de abogacia a distancia</t>
+          <t>tecnicatura en produccion agropecuaria</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C142" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -4228,33 +4475,33 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>estudiar corredor inmobiliario</t>
+          <t>cómo estudiar desde casa</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C143" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>estudiar abogacia a distancia</t>
+          <t>carrera de martillero y corredor publico</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C144" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -4266,14 +4513,14 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>universidad salta</t>
+          <t>estudiar abogacia a distancia</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C145" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -4285,14 +4532,14 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>universidad a distancia en buenos aires</t>
+          <t>universidad de salta carreras a distancia</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C146" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -4304,33 +4551,33 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>universidad de salta carreras a distancia</t>
+          <t>carreras cortas con salida laboral</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C147" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>universidad a distancia argentina</t>
+          <t>estudiar virtual</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C148" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -4342,14 +4589,14 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tecnicatura en gestion de calidad</t>
+          <t>gestion bancaria</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -4361,33 +4608,33 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>gestion bancaria</t>
+          <t>licenciatura en educacion fisica en linea</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C150" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>carreras online argentina</t>
+          <t>comercio internacional y aduanas universidades</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C151" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -4399,14 +4646,14 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>carrera gestion de calidad</t>
+          <t>licenciatura en ciencia de datos</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C152" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -4418,11 +4665,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>licenciatura en administracion de empresas en linea</t>
+          <t>estudiar seguridad informatica</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C153" t="n">
         <v>9</v>
@@ -4437,33 +4684,33 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>licenciatura en educacion fisica en linea</t>
+          <t>universidades en buenos aires</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C154" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>carrera de medio ambiente</t>
+          <t>carrera de comercio exterior</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C155" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -4475,14 +4722,14 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>enseñanza universitaria</t>
+          <t>inscripciones de universidad</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C156" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -4494,14 +4741,14 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>carrera de martillero y corredor publico</t>
+          <t>estudiar corredor inmobiliario</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C157" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -4513,14 +4760,14 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>carrera de contador publico a distancia</t>
+          <t>licenciatura en higiene y seguridad en el trabajo</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C158" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -4532,14 +4779,14 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>corredor inmobiliario a distancia</t>
+          <t>estudiar secretariado a distancia</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C159" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4551,14 +4798,14 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>estudiar derecho a distancia</t>
+          <t>carrera de abogacia a distancia</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C160" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -4570,33 +4817,33 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>escribanía distancia</t>
+          <t>procuracion a distancia</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C161" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>carrera de escribano</t>
+          <t>martillero público a distancia</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4608,14 +4855,14 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>carrera de minería</t>
+          <t>universidad a distancia en buenos aires</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -4627,14 +4874,14 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>educacion a distancia</t>
+          <t>carrera de contador publico a distancia</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D164" t="n">
         <v>0</v>
@@ -4646,14 +4893,14 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>estudiar medio ambiente</t>
+          <t>gestion educativa y gestion escolar</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -4665,14 +4912,14 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>carreras a distancia argentina</t>
+          <t>carreras con salida laboral online</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C166" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -4684,14 +4931,14 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>carreras cortas con salida laboral</t>
+          <t>gestion agropecuaria</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C167" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -4703,14 +4950,14 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>licenciatura en higiene y seguridad en el trabajo</t>
+          <t>licenciatura en recursos humanos a distancia</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C168" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -4722,14 +4969,14 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>licenciatura en recursos humanos a distancia</t>
+          <t>universidades a distancia oficiales</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C169" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -4741,14 +4988,14 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>cómo estudiar desde casa</t>
+          <t>estudios carreras</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C170" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -4760,14 +5007,14 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>cursar a distancia</t>
+          <t>estudios de criminologia</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C171" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D171" t="n">
         <v>0</v>
@@ -4779,14 +5026,14 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>gestion educativa y gestion escolar</t>
+          <t>estudiar medio ambiente</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C172" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -4798,14 +5045,14 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>gestion agropecuaria</t>
+          <t>mejores universidades online</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C173" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -4817,14 +5064,14 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>universidad de salta a distancia</t>
+          <t>licenciatura en marketing</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C174" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -4836,14 +5083,14 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>inscripciones universitarias</t>
+          <t>educación online</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C175" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -4855,14 +5102,14 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>carrera de comercio exterior</t>
+          <t>curso de guia de turismo</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C176" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D176" t="n">
         <v>0</v>
@@ -4874,14 +5121,14 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>licenciatura en relaciones internacionales a distancia</t>
+          <t>carreras cortas a distancia</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C177" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -4893,14 +5140,14 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>siglo 21 salta</t>
+          <t>carrera de medio ambiente</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C178" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
@@ -4912,14 +5159,14 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>relaciones internacionales y comercio exterior</t>
+          <t>carrera de minería</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C179" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -4931,14 +5178,14 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>qué carrera estudiar online</t>
+          <t>universidades de criminologia</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -4950,14 +5197,14 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>carrera de secretaria</t>
+          <t>títulos universitarios online</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C181" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -4969,14 +5216,14 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>carrera de economia y finanzas</t>
+          <t>facultades virtuales</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C182" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -4988,14 +5235,14 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>estudiar ciencia de datos</t>
+          <t>siglo 21 jujuy</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C183" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D183" t="n">
         <v>0</v>
@@ -5007,14 +5254,14 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>martillero público a distancia</t>
+          <t>universidades oferta de carreras</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C184" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -5026,14 +5273,14 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>marketing y comercializacion</t>
+          <t>martillero público carrera</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C185" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -5045,14 +5292,14 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>universidad online argentina</t>
+          <t>que carrera estudiar</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C186" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -5064,14 +5311,14 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>licenciatura en relaciones publicas</t>
+          <t>marketing y comercializacion</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C187" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
         <v>0</v>
@@ -5083,33 +5330,33 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>veterinaria universidad</t>
+          <t>tecnicatura en secretariado ejecutivo</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C188" t="n">
         <v>5</v>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>licenciatura en marketing</t>
+          <t>relaciones exteriores carrera</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C189" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -5121,14 +5368,14 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>estudiar procuracion</t>
+          <t>siglo 21 salta</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C190" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -5140,14 +5387,14 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>estudiar seguridad informatica</t>
+          <t>carreras con salida laboral rápida</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C191" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -5159,14 +5406,14 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>lic higiene y seguridad</t>
+          <t>universidades neuquen</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -5178,14 +5425,14 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>carreras mineras para mujeres</t>
+          <t>gestion de calidad a distancia</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C193" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -5197,11 +5444,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>martillero público carrera</t>
+          <t>relaciones internacionales y comercio exterior</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C194" t="n">
         <v>4</v>
@@ -5216,14 +5463,14 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>carreras nuevas</t>
+          <t>facultad de salta</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C195" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D195" t="n">
         <v>0</v>
@@ -5235,14 +5482,14 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>estudios de criminologia</t>
+          <t>carrera de negocios digitales</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C196" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D196" t="n">
         <v>0</v>
@@ -5254,52 +5501,52 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>licenciatura en ed fisica</t>
+          <t>lic higiene y seguridad</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E197" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>licenciatura de educacion fisica a distancia</t>
+          <t>mba ucasal</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C198" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>carrera de recursos humanos</t>
+          <t>estudiar virtualmente</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C199" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D199" t="n">
         <v>0</v>
@@ -5311,14 +5558,14 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>carrera de negocios digitales</t>
+          <t>licenciatura en relaciones internacionales a distancia</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C200" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D200" t="n">
         <v>0</v>
@@ -5330,14 +5577,14 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>procuracion a distancia</t>
+          <t>universidades virtuales argentina</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C201" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D201" t="n">
         <v>0</v>
@@ -5349,14 +5596,14 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>estudiar abogacia</t>
+          <t>siglo 21 neuquen</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C202" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D202" t="n">
         <v>0</v>
@@ -5368,14 +5615,14 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>lic educacion fisica</t>
+          <t>enseñanza universitaria</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C203" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D203" t="n">
         <v>0</v>
@@ -5387,11 +5634,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>estudiar secretariado a distancia</t>
+          <t>ahorro de energia</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C204" t="n">
         <v>4</v>
@@ -5406,52 +5653,52 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>carreras por estudiar</t>
+          <t>licenciatura de educacion fisica a distancia</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C205" t="n">
         <v>4</v>
       </c>
       <c r="D205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>universidades para estudiar</t>
+          <t>comercializacion carrera</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C206" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>licenciatura en gestión universitaria</t>
+          <t>carrera de recursos humanos</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C207" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D207" t="n">
         <v>0</v>
@@ -5463,14 +5710,14 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>estudiar carrera universitaria</t>
+          <t>ceremonial y protocolo empresarial</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D208" t="n">
         <v>0</v>
@@ -5482,14 +5729,14 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>abogacia carrera</t>
+          <t>estudiar ciencia de datos</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D209" t="n">
         <v>0</v>
@@ -5501,14 +5748,14 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ahorro de energia</t>
+          <t>inscripciones universitarias</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C210" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D210" t="n">
         <v>0</v>
@@ -5520,14 +5767,14 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>técnico en operaciones mineras</t>
+          <t>licenciatura en gestión universitaria</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D211" t="n">
         <v>0</v>
@@ -5539,14 +5786,14 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>licenciatura marketing</t>
+          <t>estudiar procuracion</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
@@ -5558,14 +5805,14 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>licenciatura en educacion fisica virtual</t>
+          <t>produccion agropecuaria</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D213" t="n">
         <v>0</v>
@@ -5577,33 +5824,33 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>carrera de criminologia a distancia</t>
+          <t>marketing universidades</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E214" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>siglo 21 neuquen</t>
+          <t>ucasal salta</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D215" t="n">
         <v>0</v>
@@ -5615,14 +5862,14 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>universidad siglo 21 salta</t>
+          <t>maestro de educacion primaria</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
@@ -5634,11 +5881,11 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>facultad de salta</t>
+          <t>derecho uba</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C217" t="n">
         <v>2</v>
@@ -5653,14 +5900,14 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>universidad higiene y seguridad</t>
+          <t>universidad online argentina</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D218" t="n">
         <v>0</v>
@@ -5672,14 +5919,14 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>las relaciones internacionales</t>
+          <t>lic en seguridad</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C219" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
@@ -5691,11 +5938,11 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>tecnicatura en secretariado ejecutivo</t>
+          <t>carrera de secretaria</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C220" t="n">
         <v>2</v>
@@ -5710,14 +5957,14 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>tecnicatura en seguridad informática</t>
+          <t>educación a distancia modalidad virtual</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C221" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D221" t="n">
         <v>0</v>
@@ -5729,14 +5976,14 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>licenciatura en recursos humanos universidades</t>
+          <t>licenciatura en relaciones publicas</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D222" t="n">
         <v>0</v>
@@ -5748,14 +5995,14 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>carreras cortas a distancia</t>
+          <t>técnico en operaciones mineras</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>
@@ -5767,14 +6014,14 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>carrera de relaciones exteriores</t>
+          <t>facultad de escribania</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D224" t="n">
         <v>0</v>
@@ -5786,14 +6033,14 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>técnico en seguridad informática</t>
+          <t>estudiar derecho a distancia</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D225" t="n">
         <v>0</v>
@@ -5805,14 +6052,14 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>carrera seguridad informatica</t>
+          <t>curso turismo</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C226" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D226" t="n">
         <v>0</v>
@@ -5824,14 +6071,14 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ucasal jujuy</t>
+          <t>cursar a distancia</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
@@ -5843,14 +6090,14 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>universidades de criminologia</t>
+          <t>estudiar mercadotecnia</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
@@ -5862,14 +6109,14 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>carrera de licenciatura en educacion fisica</t>
+          <t>carrera de economia y finanzas</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D229" t="n">
         <v>0</v>
@@ -5881,11 +6128,11 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>estudiar negocios digitales</t>
+          <t>universidad de derecho</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C230" t="n">
         <v>2</v>
@@ -5900,14 +6147,14 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>derecho uba</t>
+          <t>facultad de derecho</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D231" t="n">
         <v>0</v>
@@ -5919,14 +6166,14 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>marketing universidades</t>
+          <t>qué carrera estudiar online</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C232" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D232" t="n">
         <v>0</v>
@@ -5938,14 +6185,14 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>estudiar recursos humanos online</t>
+          <t>veterinaria universidad</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D233" t="n">
         <v>0</v>
@@ -5957,30 +6204,30 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>produccion agropecuaria</t>
+          <t>carreras nuevas</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E234" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>q carreras hay para estudiar</t>
+          <t>universidad siglo 21 jujuy</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C235" t="n">
         <v>2</v>
@@ -5995,14 +6242,14 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>licenciatura en gestion de recursos humanos</t>
+          <t>estudiar negocios digitales</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236" t="n">
         <v>0</v>
@@ -6014,14 +6261,14 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>donde estudiar procuracion</t>
+          <t>administracion de empresas universidades</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D237" t="n">
         <v>0</v>
@@ -6033,14 +6280,14 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>estudiar contador público a distancia</t>
+          <t>universidades para estudiar</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D238" t="n">
         <v>0</v>
@@ -6052,33 +6299,33 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>donde [estudiar veterinaria]</t>
+          <t>tecnico en gestion bancaria</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C239" t="n">
         <v>2</v>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>licenciatura en rrhh a distancia</t>
+          <t>tecnicatura en seguridad informática</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D240" t="n">
         <v>0</v>
@@ -6090,14 +6337,14 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>administracion en una empresa</t>
+          <t>licenciatura de relaciones internacionales</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D241" t="n">
         <v>0</v>
@@ -6109,11 +6356,11 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>licenciatura en higiene y seguridad</t>
+          <t>licenciatura en ed fisica</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
@@ -6128,14 +6375,14 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>carrera de marketing</t>
+          <t>lic educacion fisica</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D243" t="n">
         <v>0</v>
@@ -6147,14 +6394,14 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>universidad de salta neuquen</t>
+          <t>estudiar abogacia</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D244" t="n">
         <v>0</v>
@@ -6166,14 +6413,14 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>upro san luis</t>
+          <t>ucasal carreras</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D245" t="n">
         <v>0</v>
@@ -6185,14 +6432,14 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>universidades que dictan carreras a distancia</t>
+          <t>universidad de salta neuquen</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D246" t="n">
         <v>0</v>
@@ -6204,11 +6451,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>estudiar mercadotecnia</t>
+          <t>estudiar contador público a distancia</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
@@ -6223,14 +6470,14 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>administracion bancaria carrera</t>
+          <t>carreras por estudiar</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
@@ -6242,11 +6489,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>universidades neuquen</t>
+          <t>relaciones publicas</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C249" t="n">
         <v>1</v>
@@ -6261,14 +6508,14 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>estudiar recursos humanos</t>
+          <t>abogacia carrera</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D250" t="n">
         <v>0</v>
@@ -6280,11 +6527,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>gestion bancaria y financiera</t>
+          <t>carrera de relaciones exteriores</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>
@@ -6299,11 +6546,11 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>inscripciones para estudiar</t>
+          <t>carrera de criminologia a distancia</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C252" t="n">
         <v>1</v>
@@ -6318,14 +6565,14 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>administracion bancaria donde estudiar</t>
+          <t>marketing y publicidad carrera</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D253" t="n">
         <v>0</v>
@@ -6341,29 +6588,29 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E254" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>universidad siglo 21 jujuy</t>
+          <t>licenciatura en recursos humanos universidades</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D255" t="n">
         <v>0</v>
@@ -6375,14 +6622,14 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>estudiar marketing y publicidad</t>
+          <t>universidad higiene y seguridad</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D256" t="n">
         <v>0</v>
@@ -6394,14 +6641,14 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>carrera de martillero</t>
+          <t>tecnicatura bancaria</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D257" t="n">
         <v>0</v>
@@ -6413,14 +6660,14 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>carrera de contador a distancia</t>
+          <t>carrera de recursos humanos a distancia</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D258" t="n">
         <v>0</v>
@@ -6432,14 +6679,14 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>carrera de contabilidad materias</t>
+          <t>licenciatura en administración de negocios digitales</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D259" t="n">
         <v>0</v>
@@ -6451,14 +6698,14 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>universidades de administracion</t>
+          <t>donde estudiar procuracion</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D260" t="n">
         <v>0</v>
@@ -6470,14 +6717,14 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>maestro de educacion primaria</t>
+          <t>estudiar carrera universitaria</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D261" t="n">
         <v>0</v>
@@ -6489,11 +6736,11 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>inscripciones</t>
+          <t>administracion bancaria carrera</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C262" t="n">
         <v>1</v>
@@ -6508,14 +6755,14 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>licenciatura en estudios internacionales</t>
+          <t>carrera de licenciatura en educacion fisica</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D263" t="n">
         <v>0</v>
@@ -6527,11 +6774,11 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>siglo 21 jujuy</t>
+          <t>donde estudiar comercio exterior y aduanas</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C264" t="n">
         <v>1</v>
@@ -6546,14 +6793,14 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>lic en rrhh</t>
+          <t>carrera de contabilidad materias</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D265" t="n">
         <v>0</v>
@@ -6565,14 +6812,14 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>tecnico en seguros a distancia</t>
+          <t>estudiar recursos humanos</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D266" t="n">
         <v>0</v>
@@ -6584,11 +6831,11 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>carreras ucasal a distancia</t>
+          <t>tecnicatura agropecuaria a distancia</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C267" t="n">
         <v>1</v>
@@ -6603,14 +6850,14 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>tecnicatura agropecuaria a distancia</t>
+          <t>universidad católica de salta</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D268" t="n">
         <v>0</v>
@@ -6622,11 +6869,11 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>comercializacion carrera</t>
+          <t>secretariado ejecutivo online</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C269" t="n">
         <v>1</v>
@@ -6645,7 +6892,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C270" t="n">
         <v>1</v>
@@ -6660,11 +6907,11 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>licenciatura en administración de negocios digitales</t>
+          <t>licenciatura en educacion fisica virtual</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C271" t="n">
         <v>1</v>
@@ -6679,14 +6926,14 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>relaciones publicas e institucionales</t>
+          <t>carrera de contador a distancia</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
@@ -6698,11 +6945,11 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>licenciatura en comercio exterior y aduanas</t>
+          <t>tecnico en administracion agropecuaria</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C273" t="n">
         <v>1</v>
@@ -6717,14 +6964,14 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>relaciones publicas a distancia</t>
+          <t>administración de empresas</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D274" t="n">
         <v>0</v>
@@ -6736,11 +6983,11 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>relaciones publicas</t>
+          <t>escuelas de turismo</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C275" t="n">
         <v>1</v>
@@ -6755,11 +7002,11 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>tecnico en gestion bancaria</t>
+          <t>recursos humanos carrera a distancia</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C276" t="n">
         <v>1</v>
@@ -6774,11 +7021,11 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>gestion de calidad a distancia</t>
+          <t>técnico en seguridad informática</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C277" t="n">
         <v>1</v>
@@ -6793,11 +7040,11 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>formación%20profesional%20online</t>
+          <t>administracion de recursos humanos</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C278" t="n">
         <v>1</v>
@@ -6812,14 +7059,14 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>universidad de derecho</t>
+          <t>donde [estudiar veterinaria]</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D279" t="n">
         <v>0</v>
@@ -6831,14 +7078,14 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>relaciones exteriores carrera</t>
+          <t>tecnico en seguros a distancia</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D280" t="n">
         <v>0</v>
@@ -6850,14 +7097,14 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>donde estudiar economia</t>
+          <t>guia de turismo carrera</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D281" t="n">
         <v>0</v>
@@ -6869,14 +7116,14 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>carrera para bancario</t>
+          <t>licenciatura en rrhh a distancia</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D282" t="n">
         <v>0</v>
@@ -6888,11 +7135,11 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>carrera licenciatura en economia</t>
+          <t>carrera de seguros</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C283" t="n">
         <v>1</v>
@@ -6907,14 +7154,14 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>licenciatura de relaciones internacionales</t>
+          <t>inscripciones</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D284" t="n">
         <v>0</v>
@@ -6926,30 +7173,30 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>carrera diseño grafico</t>
+          <t>licenciatura recursos humanos</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E285" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>quiero estudiar economia</t>
+          <t>inscripciones para estudiar</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C286" t="n">
         <v>1</v>
@@ -6964,33 +7211,33 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ucasal salta</t>
+          <t>carrera ciencia de datos</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C287" t="n">
         <v>1</v>
       </c>
       <c r="D287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E287" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>carrera de seguros</t>
+          <t>ucasal tecnicaturas</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D288" t="n">
         <v>0</v>
@@ -7002,14 +7249,14 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>donde estudiar traductorado de ingles</t>
+          <t>carrera seguridad informatica</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D289" t="n">
         <v>0</v>
@@ -7021,38 +7268,1691 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>facultad de derecho</t>
+          <t>licenciatura en gestion de recursos humanos</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C290" t="n">
         <v>1</v>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E290" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>lic en seguridad</t>
+          <t>estudiar recursos humanos online</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D291" t="n">
         <v>0</v>
       </c>
       <c r="E291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>carrera de marketing</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>2</v>
+      </c>
+      <c r="C292" t="n">
+        <v>1</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>carrera de martillero</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>2</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>carrera de comercializacion</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>2</v>
+      </c>
+      <c r="C294" t="n">
+        <v>2</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ucasal jujuy</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>2</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ucasal distancia</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>2</v>
+      </c>
+      <c r="C296" t="n">
+        <v>1</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1</v>
+      </c>
+      <c r="E296" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>carreras ucasal</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>2</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0</v>
+      </c>
+      <c r="D297" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>carreras ucasal a distancia</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>2</v>
+      </c>
+      <c r="C298" t="n">
+        <v>1</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>q carreras hay para estudiar</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>2</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>universidad siglo 21 salta</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>2</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>licenciatura en comercio exterior y aduanas</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>2</v>
+      </c>
+      <c r="C301" t="n">
+        <v>1</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>gestion bancaria y financiera</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>2</v>
+      </c>
+      <c r="C302" t="n">
+        <v>2</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>universidad comodoro rivadavia</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>1</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ucasal abogacia</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>1</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>universidad nacional de salta</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>1</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>uces</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>1</v>
+      </c>
+      <c r="C306" t="n">
+        <v>1</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>universidad nacional de quilmes</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>1</v>
+      </c>
+      <c r="C307" t="n">
+        <v>1</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>upro san luis</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>1</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ucasal learning</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>1</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>universidad de economia</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>1</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>universidades de administracion</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>1</v>
+      </c>
+      <c r="C311" t="n">
+        <v>1</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>universidades que dictan carreras a distancia</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>1</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>universidad seguridad informatica</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>1</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>formación%20profesional%20online</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>1</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>trabajo social</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>1</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>carreras a distancia gratis</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>1</v>
+      </c>
+      <c r="C316" t="n">
+        <v>1</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>economia carrera universitaria</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>1</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>donde estudiar traductorado de ingles</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>1</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>donde estudiar licenciatura en recursos humanos</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>1</v>
+      </c>
+      <c r="C319" t="n">
+        <v>1</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>donde estudiar economia</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>1</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>donde estudiar derecho</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>1</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>cursos universidad</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>1</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>cursos gratis</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>1</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>cursos en línea</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>1</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>corredor inmobiliario</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>1</v>
+      </c>
+      <c r="C325" t="n">
+        <v>1</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>ceremonial y protocolo</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>1</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>catolica de salta</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>1</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>carreras universidad del comahue</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>1</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>carreras cortas mendoza</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>1</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>carreras</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>1</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0</v>
+      </c>
+      <c r="E330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>tecnicatura programación a distancia</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>1</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>carrera%20para%20secretaria</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>1</v>
+      </c>
+      <c r="C332" t="n">
+        <v>1</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>carrera para bancario</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>1</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>carrera licenciatura en economia</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>1</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>carrera educación física</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>1</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0</v>
+      </c>
+      <c r="E335" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>carrera de rrhh</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>1</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0</v>
+      </c>
+      <c r="E336" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>carrera de administracion bancaria</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>1</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>carrera de abogado</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>1</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>carrera abogacía</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>1</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>administración de empresas neuquén</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>1</v>
+      </c>
+      <c r="C340" t="n">
+        <v>1</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>administración agropecuaria</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>1</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>administracion universidades</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>1</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>administracion en una empresa</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>1</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>administracion bancaria donde estudiar</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>1</v>
+      </c>
+      <c r="C344" t="n">
+        <v>1</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>economia universidades</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>1</v>
+      </c>
+      <c r="C345" t="n">
+        <v>1</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>educación física a distancia</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>1</v>
+      </c>
+      <c r="C346" t="n">
+        <v>1</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>escribanía a distancia</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>1</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>escribanía carrera</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>1</v>
+      </c>
+      <c r="C348" t="n">
+        <v>1</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>seguridad e higiene</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>1</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>relaciones publicas e institucionales</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>1</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>relaciones publicas a distancia</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>1</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>recursos humanos a distancia</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>1</v>
+      </c>
+      <c r="C352" t="n">
+        <v>1</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>quiero estudiar economia</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>1</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>psicología a distancia</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>1</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>psicologia</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>1</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>profesorado educación física</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>1</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>pregrado</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>1</v>
+      </c>
+      <c r="C357" t="n">
+        <v>1</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>posgrado</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>1</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0</v>
+      </c>
+      <c r="E358" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>medicina gratis argentina</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>1</v>
+      </c>
+      <c r="C359" t="n">
+        <v>1</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>marketing siglo 21</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>1</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>licenciaturas</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>1</v>
+      </c>
+      <c r="C361" t="n">
+        <v>1</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0</v>
+      </c>
+      <c r="E361" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>licenciatura marketing</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>1</v>
+      </c>
+      <c r="C362" t="n">
+        <v>1</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>licenciatura en higiene y seguridad</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>1</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0</v>
+      </c>
+      <c r="E363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>licenciatura en estudios internacionales</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>1</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0</v>
+      </c>
+      <c r="D364" t="n">
+        <v>0</v>
+      </c>
+      <c r="E364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>licenciatura en educación a distancia</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>1</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>licenciatura en criminalística</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>1</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>licenciatura en análisis de datos</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>1</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0</v>
+      </c>
+      <c r="D367" t="n">
+        <v>0</v>
+      </c>
+      <c r="E367" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>licenciatura en administración</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>1</v>
+      </c>
+      <c r="C368" t="n">
+        <v>1</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0</v>
+      </c>
+      <c r="E368" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>licenciatura comercio internacional</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>1</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0</v>
+      </c>
+      <c r="E369" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>lic en rrhh</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>1</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0</v>
+      </c>
+      <c r="E370" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>las relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>1</v>
+      </c>
+      <c r="C371" t="n">
+        <v>0</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0</v>
+      </c>
+      <c r="E371" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>estudios bancarios</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>1</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0</v>
+      </c>
+      <c r="E372" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>estudiar marketing y publicidad</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>1</v>
+      </c>
+      <c r="C373" t="n">
+        <v>1</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0</v>
+      </c>
+      <c r="E373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>estudiar guia de turismo</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>1</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0</v>
+      </c>
+      <c r="D374" t="n">
+        <v>0</v>
+      </c>
+      <c r="E374" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>estudiar</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>1</v>
+      </c>
+      <c r="C375" t="n">
+        <v>0</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0</v>
+      </c>
+      <c r="E375" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>especialidad seguridad e higiene</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>1</v>
+      </c>
+      <c r="C376" t="n">
+        <v>0</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>administración agraria</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>0</v>
+      </c>
+      <c r="C377" t="n">
+        <v>1</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0</v>
+      </c>
+      <c r="E377" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>licenciatura en marketing a distancia</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>0</v>
+      </c>
+      <c r="C378" t="n">
+        <v>1</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0</v>
+      </c>
+      <c r="E378" t="n">
         <v>0</v>
       </c>
     </row>

--- a/marketing_report/outputs/Grado_Pregrado/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="453">
   <si>
     <t>UtmCampaign</t>
   </si>
@@ -72,12 +72,12 @@
     <t>15360035696</t>
   </si>
   <si>
+    <t>14892996169</t>
+  </si>
+  <si>
     <t>21772187688</t>
   </si>
   <si>
-    <t>14892996169</t>
-  </si>
-  <si>
     <t>14899816755</t>
   </si>
   <si>
@@ -96,12 +96,12 @@
     <t>14905247697</t>
   </si>
   <si>
+    <t>14891543883</t>
+  </si>
+  <si>
     <t>23497387174</t>
   </si>
   <si>
-    <t>14891543883</t>
-  </si>
-  <si>
     <t>14906054625</t>
   </si>
   <si>
@@ -117,19 +117,22 @@
     <t>14909096324</t>
   </si>
   <si>
+    <t>14894392756</t>
+  </si>
+  <si>
     <t>14894109331</t>
   </si>
   <si>
-    <t>14894392756</t>
-  </si>
-  <si>
     <t>15232856055</t>
   </si>
   <si>
+    <t>16552752228</t>
+  </si>
+  <si>
     <t>22644502976</t>
   </si>
   <si>
-    <t>16552752228</t>
+    <t>23277494379</t>
   </si>
   <si>
     <t>14905339848</t>
@@ -147,9 +150,6 @@
     <t>14905619205</t>
   </si>
   <si>
-    <t>23277494379</t>
-  </si>
-  <si>
     <t>16515402374</t>
   </si>
   <si>
@@ -159,63 +159,66 @@
     <t>22647879775</t>
   </si>
   <si>
+    <t>20998371077</t>
+  </si>
+  <si>
     <t>22758675353</t>
   </si>
   <si>
-    <t>20998371077</t>
-  </si>
-  <si>
     <t>20531309410</t>
   </si>
   <si>
+    <t>15773753483</t>
+  </si>
+  <si>
     <t>15034800468</t>
   </si>
   <si>
     <t>20523462698</t>
   </si>
   <si>
+    <t>15034827564</t>
+  </si>
+  <si>
+    <t>23041074431</t>
+  </si>
+  <si>
+    <t>22637500317</t>
+  </si>
+  <si>
+    <t>14941637467</t>
+  </si>
+  <si>
     <t>21778508075</t>
   </si>
   <si>
-    <t>22637500317</t>
-  </si>
-  <si>
-    <t>23041074431</t>
+    <t>21996147342</t>
   </si>
   <si>
     <t>21933203642</t>
   </si>
   <si>
-    <t>21996147342</t>
+    <t>23255356694</t>
+  </si>
+  <si>
+    <t>branding</t>
+  </si>
+  <si>
+    <t>15069068625</t>
   </si>
   <si>
     <t>20998490630</t>
   </si>
   <si>
-    <t>15069068625</t>
-  </si>
-  <si>
-    <t>branding</t>
-  </si>
-  <si>
-    <t>14941637467</t>
-  </si>
-  <si>
-    <t>15034827564</t>
+    <t>23220287690</t>
+  </si>
+  <si>
+    <t>12018552619</t>
   </si>
   <si>
     <t>23040805580</t>
   </si>
   <si>
-    <t>23255356694</t>
-  </si>
-  <si>
-    <t>15773753483</t>
-  </si>
-  <si>
-    <t>12018552619</t>
-  </si>
-  <si>
     <t>22454462079</t>
   </si>
   <si>
@@ -255,10 +258,13 @@
     <t>universidad virtual</t>
   </si>
   <si>
+    <t>licenciatura en educacion fisica y deportes</t>
+  </si>
+  <si>
     <t>carrera de higiene y seguridad</t>
   </si>
   <si>
-    <t>licenciatura en educacion fisica y deportes</t>
+    <t>carreras universitarias a distancia</t>
   </si>
   <si>
     <t>estudiar escribania</t>
@@ -267,9 +273,6 @@
     <t>carreras online</t>
   </si>
   <si>
-    <t>carreras universitarias a distancia</t>
-  </si>
-  <si>
     <t>abogacia a distancia</t>
   </si>
   <si>
@@ -282,27 +285,27 @@
     <t>licenciatura en seguridad</t>
   </si>
   <si>
+    <t>carreras cortas virtuales</t>
+  </si>
+  <si>
     <t>estudiar contabilidad</t>
   </si>
   <si>
+    <t>licenciatura en gestión educativa</t>
+  </si>
+  <si>
+    <t>ciberseguridad carrera</t>
+  </si>
+  <si>
+    <t>estudiar gestion de calidad</t>
+  </si>
+  <si>
     <t>universidad de salta</t>
   </si>
   <si>
-    <t>carreras cortas virtuales</t>
-  </si>
-  <si>
     <t>universidad de quilmes</t>
   </si>
   <si>
-    <t>licenciatura en gestión educativa</t>
-  </si>
-  <si>
-    <t>estudiar gestion de calidad</t>
-  </si>
-  <si>
-    <t>ciberseguridad carrera</t>
-  </si>
-  <si>
     <t>formación profesional online</t>
   </si>
   <si>
@@ -312,21 +315,21 @@
     <t>carrera de procurador</t>
   </si>
   <si>
+    <t>carreras virtuales</t>
+  </si>
+  <si>
+    <t>estudiar a distancia en argentina</t>
+  </si>
+  <si>
+    <t>recursos humanos</t>
+  </si>
+  <si>
     <t>estudiar comercio internacional</t>
   </si>
   <si>
     <t>corredor inmobiliario carrera</t>
   </si>
   <si>
-    <t>estudiar a distancia en argentina</t>
-  </si>
-  <si>
-    <t>carreras virtuales</t>
-  </si>
-  <si>
-    <t>recursos humanos</t>
-  </si>
-  <si>
     <t>carrera de derecho</t>
   </si>
   <si>
@@ -345,43 +348,46 @@
     <t>ucasal abogacia a distancia</t>
   </si>
   <si>
+    <t>ingeniería en minas</t>
+  </si>
+  <si>
+    <t>relaciones internacionales carrera</t>
+  </si>
+  <si>
+    <t>administracion de empresas agropecuarias</t>
+  </si>
+  <si>
     <t>carreras a distancia</t>
   </si>
   <si>
-    <t>ingeniería en minas</t>
-  </si>
-  <si>
-    <t>relaciones internacionales carrera</t>
-  </si>
-  <si>
-    <t>administracion de empresas agropecuarias</t>
+    <t>licenciatura en administracion de empresas</t>
   </si>
   <si>
     <t>carrera martillero publico a distancia</t>
   </si>
   <si>
-    <t>licenciatura en administracion de empresas</t>
-  </si>
-  <si>
     <t>estudiar agente inmobiliario</t>
   </si>
   <si>
     <t>abogacia</t>
   </si>
   <si>
+    <t>licenciatura en entrenamiento deportivo</t>
+  </si>
+  <si>
+    <t>administracion bancaria</t>
+  </si>
+  <si>
+    <t>ciencia de datos</t>
+  </si>
+  <si>
     <t>martillero corredor público y corredor inmobiliario</t>
   </si>
   <si>
-    <t>administracion bancaria</t>
-  </si>
-  <si>
-    <t>ciencia de datos</t>
-  </si>
-  <si>
     <t>universidad kennedy</t>
   </si>
   <si>
-    <t>licenciatura en entrenamiento deportivo</t>
+    <t>facultades online en argentina</t>
   </si>
   <si>
     <t>estudiar seguridad</t>
@@ -390,57 +396,54 @@
     <t>contador carrera</t>
   </si>
   <si>
+    <t>tecnico en operaciones mineras</t>
+  </si>
+  <si>
     <t>universidad siglo 21</t>
   </si>
   <si>
-    <t>tecnico en operaciones mineras</t>
-  </si>
-  <si>
-    <t>facultades online en argentina</t>
-  </si>
-  <si>
     <t>educación superior virtual</t>
   </si>
   <si>
     <t>estudios con salida laboral</t>
   </si>
   <si>
+    <t>cursos universitarios a distancia</t>
+  </si>
+  <si>
+    <t>licenciatura de seguridad publica</t>
+  </si>
+  <si>
     <t>siglo 21</t>
   </si>
   <si>
-    <t>cursos universitarios a distancia</t>
-  </si>
-  <si>
-    <t>licenciatura de seguridad publica</t>
+    <t>secretariado administrativo online</t>
   </si>
   <si>
     <t>ucasal a distancia</t>
   </si>
   <si>
-    <t>secretariado administrativo online</t>
+    <t>recursos humanos carrera</t>
+  </si>
+  <si>
+    <t>carrera de economia</t>
   </si>
   <si>
     <t>universidades en jujuy</t>
   </si>
   <si>
-    <t>recursos humanos carrera</t>
+    <t>que estudiar para ser agente inmobiliario</t>
   </si>
   <si>
     <t>estudiar martillero publico</t>
   </si>
   <si>
-    <t>que estudiar para ser agente inmobiliario</t>
-  </si>
-  <si>
-    <t>carrera de economia</t>
+    <t>estudiar secretariado</t>
   </si>
   <si>
     <t>universidades en misiones</t>
   </si>
   <si>
-    <t>estudiar secretariado</t>
-  </si>
-  <si>
     <t>carreras energias renovables</t>
   </si>
   <si>
@@ -462,18 +465,21 @@
     <t>marketing digital carrera</t>
   </si>
   <si>
+    <t>carreras universitarias online</t>
+  </si>
+  <si>
+    <t>comercio exterior carrera</t>
+  </si>
+  <si>
     <t>universidad a distancia</t>
   </si>
   <si>
-    <t>comercio exterior carrera</t>
+    <t>opciones para estudiar online</t>
   </si>
   <si>
     <t>economia carrera</t>
   </si>
   <si>
-    <t>opciones para estudiar online</t>
-  </si>
-  <si>
     <t>curso de banca y finanzas</t>
   </si>
   <si>
@@ -483,13 +489,19 @@
     <t>tecnicatura en ceremonial y protocolo</t>
   </si>
   <si>
-    <t>carreras universitarias online</t>
+    <t>marketing carrera</t>
+  </si>
+  <si>
+    <t>licenciatura a distancia</t>
   </si>
   <si>
     <t>negocios digitales</t>
   </si>
   <si>
-    <t>marketing carrera</t>
+    <t>carreras universitarias virtuales</t>
+  </si>
+  <si>
+    <t>universidad online</t>
   </si>
   <si>
     <t>estudiar criminología</t>
@@ -501,30 +513,21 @@
     <t>carrera en seguridad</t>
   </si>
   <si>
-    <t>universidad online</t>
-  </si>
-  <si>
-    <t>licenciatura a distancia</t>
-  </si>
-  <si>
-    <t>carreras universitarias virtuales</t>
-  </si>
-  <si>
     <t>escribania ucasal</t>
   </si>
   <si>
     <t>técnico en mineria</t>
   </si>
   <si>
+    <t>universidades en neuquen</t>
+  </si>
+  <si>
+    <t>estudiar ciberseguridad</t>
+  </si>
+  <si>
     <t>educacion a distancia</t>
   </si>
   <si>
-    <t>universidades en neuquen</t>
-  </si>
-  <si>
-    <t>estudiar ciberseguridad</t>
-  </si>
-  <si>
     <t>carreras online argentina</t>
   </si>
   <si>
@@ -534,42 +537,42 @@
     <t>criminología universidades</t>
   </si>
   <si>
+    <t>tecnico agropecuario a distancia</t>
+  </si>
+  <si>
     <t>carrera de administracion</t>
   </si>
   <si>
-    <t>tecnico agropecuario a distancia</t>
-  </si>
-  <si>
     <t>estudiar licenciatura</t>
   </si>
   <si>
+    <t>licenciatura en administración agraria</t>
+  </si>
+  <si>
     <t>estudiar mineria</t>
   </si>
   <si>
-    <t>licenciatura en administración agraria</t>
+    <t>educación superior a distancia</t>
+  </si>
+  <si>
+    <t>estudiar y trabajar a la vez</t>
+  </si>
+  <si>
+    <t>estudios online universitarios</t>
+  </si>
+  <si>
+    <t>licenciatura en recursos humanos</t>
   </si>
   <si>
     <t>universidades en salta</t>
   </si>
   <si>
-    <t>estudios online universitarios</t>
-  </si>
-  <si>
-    <t>licenciatura en recursos humanos</t>
-  </si>
-  <si>
-    <t>estudiar y trabajar a la vez</t>
-  </si>
-  <si>
-    <t>educación superior a distancia</t>
+    <t>licenciatura en actividad fisica y deporte</t>
   </si>
   <si>
     <t>estudiar marketing</t>
   </si>
   <si>
-    <t>licenciatura en actividad fisica y deporte</t>
-  </si>
-  <si>
     <t>modalidad virtual universitaria</t>
   </si>
   <si>
@@ -579,57 +582,57 @@
     <t>estudiar licenciatura en educacion fisica</t>
   </si>
   <si>
+    <t>carrera de protocolo</t>
+  </si>
+  <si>
+    <t>carrera de relaciones publicas</t>
+  </si>
+  <si>
+    <t>carreras bancarias</t>
+  </si>
+  <si>
+    <t>las carreras universitarias</t>
+  </si>
+  <si>
     <t>unsa</t>
   </si>
   <si>
-    <t>las carreras universitarias</t>
-  </si>
-  <si>
-    <t>carreras bancarias</t>
-  </si>
-  <si>
     <t>carreras agropecuarias a distancia</t>
   </si>
   <si>
+    <t>licenciatura en seguridad ciudadana</t>
+  </si>
+  <si>
+    <t>carrera gestion educativa</t>
+  </si>
+  <si>
     <t>licenciatura en economia a distancia</t>
   </si>
   <si>
     <t>relaciones publicas carrera</t>
   </si>
   <si>
-    <t>carrera de protocolo</t>
-  </si>
-  <si>
-    <t>carrera de relaciones publicas</t>
-  </si>
-  <si>
-    <t>licenciatura en seguridad ciudadana</t>
-  </si>
-  <si>
-    <t>carrera gestion educativa</t>
+    <t>carreras a distancia argentina</t>
   </si>
   <si>
     <t>universidad salta</t>
   </si>
   <si>
-    <t>carreras a distancia argentina</t>
+    <t>abogacia siglo 21</t>
+  </si>
+  <si>
+    <t>licenciatura en administracion de empresas en linea</t>
   </si>
   <si>
     <t>universidad a distancia argentina</t>
   </si>
   <si>
-    <t>licenciatura en administracion de empresas en linea</t>
-  </si>
-  <si>
-    <t>abogacia siglo 21</t>
+    <t>carreras agropecuarias</t>
   </si>
   <si>
     <t>carrera de escribano</t>
   </si>
   <si>
-    <t>carreras agropecuarias</t>
-  </si>
-  <si>
     <t>escribanía distancia</t>
   </si>
   <si>
@@ -639,127 +642,136 @@
     <t>carrera de comercio exterior y aduanas</t>
   </si>
   <si>
+    <t>carrera gestion de calidad</t>
+  </si>
+  <si>
+    <t>universidades online argentina</t>
+  </si>
+  <si>
     <t>corredor inmobiliario a distancia</t>
   </si>
   <si>
-    <t>carrera gestion de calidad</t>
-  </si>
-  <si>
-    <t>universidades online argentina</t>
-  </si>
-  <si>
     <t>carrera de bancario</t>
   </si>
   <si>
     <t>universidad de salta a distancia</t>
   </si>
   <si>
+    <t>cómo estudiar desde casa</t>
+  </si>
+  <si>
     <t>carreras mineras para mujeres</t>
   </si>
   <si>
+    <t>tecnicatura en produccion agropecuaria</t>
+  </si>
+  <si>
     <t>tecnicatura en gestion de calidad</t>
   </si>
   <si>
-    <t>tecnicatura en produccion agropecuaria</t>
-  </si>
-  <si>
-    <t>cómo estudiar desde casa</t>
-  </si>
-  <si>
     <t>carrera de martillero y corredor publico</t>
   </si>
   <si>
+    <t>estudiar virtual</t>
+  </si>
+  <si>
+    <t>comercio internacional y aduanas universidades</t>
+  </si>
+  <si>
+    <t>gestion bancaria</t>
+  </si>
+  <si>
+    <t>universidad de salta carreras a distancia</t>
+  </si>
+  <si>
+    <t>carreras cortas con salida laboral</t>
+  </si>
+  <si>
     <t>estudiar abogacia a distancia</t>
   </si>
   <si>
-    <t>universidad de salta carreras a distancia</t>
-  </si>
-  <si>
-    <t>carreras cortas con salida laboral</t>
-  </si>
-  <si>
-    <t>estudiar virtual</t>
-  </si>
-  <si>
-    <t>gestion bancaria</t>
+    <t>estudiar seguridad informatica</t>
+  </si>
+  <si>
+    <t>licenciatura en ciencia de datos</t>
   </si>
   <si>
     <t>licenciatura en educacion fisica en linea</t>
   </si>
   <si>
-    <t>comercio internacional y aduanas universidades</t>
-  </si>
-  <si>
-    <t>licenciatura en ciencia de datos</t>
-  </si>
-  <si>
-    <t>estudiar seguridad informatica</t>
+    <t>estudiar secretariado a distancia</t>
+  </si>
+  <si>
+    <t>carreras con salida laboral online</t>
+  </si>
+  <si>
+    <t>carrera de comercio exterior</t>
+  </si>
+  <si>
+    <t>procuracion a distancia</t>
+  </si>
+  <si>
+    <t>estudiar corredor inmobiliario</t>
+  </si>
+  <si>
+    <t>inscripciones de universidad</t>
   </si>
   <si>
     <t>universidades en buenos aires</t>
   </si>
   <si>
-    <t>carrera de comercio exterior</t>
-  </si>
-  <si>
-    <t>inscripciones de universidad</t>
-  </si>
-  <si>
-    <t>estudiar corredor inmobiliario</t>
+    <t>carrera de contador publico a distancia</t>
+  </si>
+  <si>
+    <t>martillero público a distancia</t>
+  </si>
+  <si>
+    <t>carrera de abogacia a distancia</t>
+  </si>
+  <si>
+    <t>gestion educativa y gestion escolar</t>
   </si>
   <si>
     <t>licenciatura en higiene y seguridad en el trabajo</t>
   </si>
   <si>
-    <t>estudiar secretariado a distancia</t>
-  </si>
-  <si>
-    <t>carrera de abogacia a distancia</t>
-  </si>
-  <si>
-    <t>procuracion a distancia</t>
-  </si>
-  <si>
-    <t>martillero público a distancia</t>
-  </si>
-  <si>
     <t>universidad a distancia en buenos aires</t>
   </si>
   <si>
-    <t>carrera de contador publico a distancia</t>
-  </si>
-  <si>
-    <t>gestion educativa y gestion escolar</t>
-  </si>
-  <si>
-    <t>carreras con salida laboral online</t>
+    <t>estudios de criminologia</t>
+  </si>
+  <si>
+    <t>licenciatura en recursos humanos a distancia</t>
+  </si>
+  <si>
+    <t>universidades a distancia oficiales</t>
+  </si>
+  <si>
+    <t>estudios carreras</t>
   </si>
   <si>
     <t>gestion agropecuaria</t>
   </si>
   <si>
-    <t>licenciatura en recursos humanos a distancia</t>
-  </si>
-  <si>
-    <t>universidades a distancia oficiales</t>
-  </si>
-  <si>
-    <t>estudios carreras</t>
-  </si>
-  <si>
-    <t>estudios de criminologia</t>
+    <t>licenciatura en marketing</t>
+  </si>
+  <si>
+    <t>educación online</t>
   </si>
   <si>
     <t>estudiar medio ambiente</t>
   </si>
   <si>
+    <t>títulos universitarios online</t>
+  </si>
+  <si>
     <t>mejores universidades online</t>
   </si>
   <si>
-    <t>licenciatura en marketing</t>
-  </si>
-  <si>
-    <t>educación online</t>
+    <t>carrera de minería</t>
+  </si>
+  <si>
+    <t>carrera de medio ambiente</t>
   </si>
   <si>
     <t>curso de guia de turismo</t>
@@ -768,16 +780,10 @@
     <t>carreras cortas a distancia</t>
   </si>
   <si>
-    <t>carrera de medio ambiente</t>
-  </si>
-  <si>
-    <t>carrera de minería</t>
-  </si>
-  <si>
     <t>universidades de criminologia</t>
   </si>
   <si>
-    <t>títulos universitarios online</t>
+    <t>martillero público carrera</t>
   </si>
   <si>
     <t>facultades virtuales</t>
@@ -789,13 +795,16 @@
     <t>universidades oferta de carreras</t>
   </si>
   <si>
-    <t>martillero público carrera</t>
+    <t>marketing y comercializacion</t>
   </si>
   <si>
     <t>que carrera estudiar</t>
   </si>
   <si>
-    <t>marketing y comercializacion</t>
+    <t>siglo 21 salta</t>
+  </si>
+  <si>
+    <t>carreras con salida laboral rápida</t>
   </si>
   <si>
     <t>tecnicatura en secretariado ejecutivo</t>
@@ -804,565 +813,565 @@
     <t>relaciones exteriores carrera</t>
   </si>
   <si>
-    <t>siglo 21 salta</t>
-  </si>
-  <si>
-    <t>carreras con salida laboral rápida</t>
+    <t>facultad de salta</t>
+  </si>
+  <si>
+    <t>gestion de calidad a distancia</t>
   </si>
   <si>
     <t>universidades neuquen</t>
   </si>
   <si>
-    <t>gestion de calidad a distancia</t>
+    <t>licenciatura en relaciones internacionales a distancia</t>
   </si>
   <si>
     <t>relaciones internacionales y comercio exterior</t>
   </si>
   <si>
-    <t>facultad de salta</t>
+    <t>estudiar virtualmente</t>
   </si>
   <si>
     <t>carrera de negocios digitales</t>
   </si>
   <si>
+    <t>enseñanza universitaria</t>
+  </si>
+  <si>
+    <t>mba ucasal</t>
+  </si>
+  <si>
+    <t>siglo 21 neuquen</t>
+  </si>
+  <si>
+    <t>universidades virtuales argentina</t>
+  </si>
+  <si>
+    <t>ahorro de energia</t>
+  </si>
+  <si>
+    <t>estudiar procuracion</t>
+  </si>
+  <si>
     <t>lic higiene y seguridad</t>
   </si>
   <si>
-    <t>mba ucasal</t>
-  </si>
-  <si>
-    <t>estudiar virtualmente</t>
-  </si>
-  <si>
-    <t>licenciatura en relaciones internacionales a distancia</t>
-  </si>
-  <si>
-    <t>universidades virtuales argentina</t>
-  </si>
-  <si>
-    <t>siglo 21 neuquen</t>
-  </si>
-  <si>
-    <t>enseñanza universitaria</t>
-  </si>
-  <si>
-    <t>ahorro de energia</t>
-  </si>
-  <si>
     <t>licenciatura de educacion fisica a distancia</t>
   </si>
   <si>
+    <t>carrera de recursos humanos</t>
+  </si>
+  <si>
+    <t>estudiar ciencia de datos</t>
+  </si>
+  <si>
+    <t>ceremonial y protocolo empresarial</t>
+  </si>
+  <si>
+    <t>inscripciones universitarias</t>
+  </si>
+  <si>
     <t>comercializacion carrera</t>
   </si>
   <si>
-    <t>carrera de recursos humanos</t>
-  </si>
-  <si>
-    <t>ceremonial y protocolo empresarial</t>
-  </si>
-  <si>
-    <t>estudiar ciencia de datos</t>
-  </si>
-  <si>
-    <t>inscripciones universitarias</t>
-  </si>
-  <si>
     <t>licenciatura en gestión universitaria</t>
   </si>
   <si>
-    <t>estudiar procuracion</t>
+    <t>lic en seguridad</t>
+  </si>
+  <si>
+    <t>carrera de secretaria</t>
+  </si>
+  <si>
+    <t>derecho uba</t>
+  </si>
+  <si>
+    <t>ucasal salta</t>
+  </si>
+  <si>
+    <t>estudiar derecho a distancia</t>
+  </si>
+  <si>
+    <t>universidad online argentina</t>
+  </si>
+  <si>
+    <t>educación a distancia modalidad virtual</t>
+  </si>
+  <si>
+    <t>maestro de educacion primaria</t>
+  </si>
+  <si>
+    <t>marketing universidades</t>
   </si>
   <si>
     <t>produccion agropecuaria</t>
   </si>
   <si>
-    <t>marketing universidades</t>
-  </si>
-  <si>
-    <t>ucasal salta</t>
-  </si>
-  <si>
-    <t>maestro de educacion primaria</t>
-  </si>
-  <si>
-    <t>derecho uba</t>
-  </si>
-  <si>
-    <t>universidad online argentina</t>
-  </si>
-  <si>
-    <t>lic en seguridad</t>
-  </si>
-  <si>
-    <t>carrera de secretaria</t>
-  </si>
-  <si>
-    <t>educación a distancia modalidad virtual</t>
+    <t>cursar a distancia</t>
+  </si>
+  <si>
+    <t>lic educacion fisica</t>
   </si>
   <si>
     <t>licenciatura en relaciones publicas</t>
   </si>
   <si>
+    <t>carrera de criminologia a distancia</t>
+  </si>
+  <si>
     <t>técnico en operaciones mineras</t>
   </si>
   <si>
+    <t>curso turismo</t>
+  </si>
+  <si>
     <t>facultad de escribania</t>
   </si>
   <si>
-    <t>estudiar derecho a distancia</t>
-  </si>
-  <si>
-    <t>curso turismo</t>
-  </si>
-  <si>
-    <t>cursar a distancia</t>
+    <t>qué carrera estudiar online</t>
+  </si>
+  <si>
+    <t>carrera de economia y finanzas</t>
+  </si>
+  <si>
+    <t>universidad de derecho</t>
+  </si>
+  <si>
+    <t>carreras nuevas</t>
+  </si>
+  <si>
+    <t>tecnicatura en seguridad informática</t>
+  </si>
+  <si>
+    <t>licenciatura de relaciones internacionales</t>
+  </si>
+  <si>
+    <t>facultad de derecho</t>
+  </si>
+  <si>
+    <t>tecnico en gestion bancaria</t>
+  </si>
+  <si>
+    <t>veterinaria universidad</t>
+  </si>
+  <si>
+    <t>gestion de bancos y empresas financieras</t>
   </si>
   <si>
     <t>estudiar mercadotecnia</t>
   </si>
   <si>
-    <t>carrera de economia y finanzas</t>
-  </si>
-  <si>
-    <t>universidad de derecho</t>
-  </si>
-  <si>
-    <t>facultad de derecho</t>
-  </si>
-  <si>
-    <t>qué carrera estudiar online</t>
-  </si>
-  <si>
-    <t>veterinaria universidad</t>
-  </si>
-  <si>
-    <t>carreras nuevas</t>
+    <t>administracion de empresas universidades</t>
+  </si>
+  <si>
+    <t>licenciatura en ed fisica</t>
+  </si>
+  <si>
+    <t>estudiar negocios digitales</t>
   </si>
   <si>
     <t>universidad siglo 21 jujuy</t>
   </si>
   <si>
-    <t>estudiar negocios digitales</t>
-  </si>
-  <si>
-    <t>administracion de empresas universidades</t>
+    <t>tecnicatura bancaria</t>
   </si>
   <si>
     <t>universidades para estudiar</t>
   </si>
   <si>
-    <t>tecnico en gestion bancaria</t>
-  </si>
-  <si>
-    <t>tecnicatura en seguridad informática</t>
-  </si>
-  <si>
-    <t>licenciatura de relaciones internacionales</t>
-  </si>
-  <si>
-    <t>licenciatura en ed fisica</t>
-  </si>
-  <si>
-    <t>lic educacion fisica</t>
+    <t>marketing y publicidad carrera</t>
+  </si>
+  <si>
+    <t>secretariado ejecutivo online</t>
+  </si>
+  <si>
+    <t>universidad higiene y seguridad</t>
+  </si>
+  <si>
+    <t>estudiar contador público a distancia</t>
+  </si>
+  <si>
+    <t>ucasal carreras</t>
+  </si>
+  <si>
+    <t>carrera de relaciones exteriores</t>
   </si>
   <si>
     <t>estudiar abogacia</t>
   </si>
   <si>
-    <t>ucasal carreras</t>
+    <t>carrera de martillero</t>
+  </si>
+  <si>
+    <t>relaciones publicas</t>
   </si>
   <si>
     <t>universidad de salta neuquen</t>
   </si>
   <si>
-    <t>estudiar contador público a distancia</t>
+    <t>abogacia carrera</t>
+  </si>
+  <si>
+    <t>licenciatura en recursos humanos universidades</t>
   </si>
   <si>
     <t>carreras por estudiar</t>
   </si>
   <si>
-    <t>relaciones publicas</t>
-  </si>
-  <si>
-    <t>abogacia carrera</t>
-  </si>
-  <si>
-    <t>carrera de relaciones exteriores</t>
-  </si>
-  <si>
-    <t>carrera de criminologia a distancia</t>
-  </si>
-  <si>
-    <t>marketing y publicidad carrera</t>
-  </si>
-  <si>
-    <t>gestion de bancos y empresas financieras</t>
-  </si>
-  <si>
-    <t>licenciatura en recursos humanos universidades</t>
-  </si>
-  <si>
-    <t>universidad higiene y seguridad</t>
-  </si>
-  <si>
-    <t>tecnicatura bancaria</t>
+    <t>donde estudiar comercio exterior y aduanas</t>
+  </si>
+  <si>
+    <t>universidad católica de salta</t>
+  </si>
+  <si>
+    <t>tecnicatura agropecuaria a distancia</t>
+  </si>
+  <si>
+    <t>estudiar recursos humanos</t>
+  </si>
+  <si>
+    <t>facultad de economia</t>
+  </si>
+  <si>
+    <t>psicologia</t>
+  </si>
+  <si>
+    <t>carrera de contabilidad materias</t>
+  </si>
+  <si>
+    <t>estudios bancarios</t>
+  </si>
+  <si>
+    <t>carrera de contador a distancia</t>
+  </si>
+  <si>
+    <t>licenciatura en educacion fisica virtual</t>
+  </si>
+  <si>
+    <t>carrera de licenciatura en educacion fisica</t>
+  </si>
+  <si>
+    <t>estudiar carrera universitaria</t>
   </si>
   <si>
     <t>carrera de recursos humanos a distancia</t>
   </si>
   <si>
+    <t>administracion bancaria carrera</t>
+  </si>
+  <si>
     <t>licenciatura en administración de negocios digitales</t>
   </si>
   <si>
     <t>donde estudiar procuracion</t>
   </si>
   <si>
-    <t>estudiar carrera universitaria</t>
-  </si>
-  <si>
-    <t>administracion bancaria carrera</t>
-  </si>
-  <si>
-    <t>carrera de licenciatura en educacion fisica</t>
-  </si>
-  <si>
-    <t>donde estudiar comercio exterior y aduanas</t>
-  </si>
-  <si>
-    <t>carrera de contabilidad materias</t>
-  </si>
-  <si>
-    <t>estudiar recursos humanos</t>
-  </si>
-  <si>
-    <t>tecnicatura agropecuaria a distancia</t>
-  </si>
-  <si>
-    <t>universidad católica de salta</t>
-  </si>
-  <si>
-    <t>secretariado ejecutivo online</t>
-  </si>
-  <si>
-    <t>facultad de economia</t>
-  </si>
-  <si>
-    <t>licenciatura en educacion fisica virtual</t>
-  </si>
-  <si>
-    <t>carrera de contador a distancia</t>
+    <t>ucasal distancia</t>
+  </si>
+  <si>
+    <t>ucasal jujuy</t>
+  </si>
+  <si>
+    <t>carrera de marketing</t>
+  </si>
+  <si>
+    <t>tecnico en seguros a distancia</t>
   </si>
   <si>
     <t>tecnico en administracion agropecuaria</t>
   </si>
   <si>
+    <t>carrera de seguros</t>
+  </si>
+  <si>
+    <t>ucasal tecnicaturas</t>
+  </si>
+  <si>
+    <t>carrera seguridad informatica</t>
+  </si>
+  <si>
+    <t>técnico en seguridad informática</t>
+  </si>
+  <si>
+    <t>estudiar recursos humanos online</t>
+  </si>
+  <si>
+    <t>recursos humanos carrera a distancia</t>
+  </si>
+  <si>
+    <t>inscripciones</t>
+  </si>
+  <si>
+    <t>administracion de recursos humanos</t>
+  </si>
+  <si>
     <t>administración de empresas</t>
   </si>
   <si>
+    <t>universidad siglo 21 salta</t>
+  </si>
+  <si>
+    <t>inscripciones para estudiar</t>
+  </si>
+  <si>
+    <t>licenciatura en estudios internacionales</t>
+  </si>
+  <si>
+    <t>licenciatura en gestion de recursos humanos</t>
+  </si>
+  <si>
     <t>escuelas de turismo</t>
   </si>
   <si>
-    <t>recursos humanos carrera a distancia</t>
-  </si>
-  <si>
-    <t>técnico en seguridad informática</t>
-  </si>
-  <si>
-    <t>administracion de recursos humanos</t>
+    <t>licenciatura en higiene y seguridad</t>
   </si>
   <si>
     <t>donde [estudiar veterinaria]</t>
   </si>
   <si>
-    <t>tecnico en seguros a distancia</t>
+    <t>licenciatura en rrhh a distancia</t>
+  </si>
+  <si>
+    <t>licenciatura recursos humanos</t>
+  </si>
+  <si>
+    <t>carrera ciencia de datos</t>
   </si>
   <si>
     <t>guia de turismo carrera</t>
   </si>
   <si>
-    <t>licenciatura en rrhh a distancia</t>
-  </si>
-  <si>
-    <t>carrera de seguros</t>
-  </si>
-  <si>
-    <t>inscripciones</t>
-  </si>
-  <si>
-    <t>licenciatura recursos humanos</t>
-  </si>
-  <si>
-    <t>inscripciones para estudiar</t>
-  </si>
-  <si>
-    <t>carrera ciencia de datos</t>
-  </si>
-  <si>
-    <t>ucasal tecnicaturas</t>
-  </si>
-  <si>
-    <t>carrera seguridad informatica</t>
-  </si>
-  <si>
-    <t>licenciatura en gestion de recursos humanos</t>
-  </si>
-  <si>
-    <t>estudiar recursos humanos online</t>
-  </si>
-  <si>
-    <t>carrera de marketing</t>
-  </si>
-  <si>
-    <t>carrera de martillero</t>
+    <t>gestion bancaria y financiera</t>
   </si>
   <si>
     <t>carrera de comercializacion</t>
   </si>
   <si>
-    <t>ucasal jujuy</t>
-  </si>
-  <si>
-    <t>ucasal distancia</t>
+    <t>carreras ucasal a distancia</t>
+  </si>
+  <si>
+    <t>q carreras hay para estudiar</t>
   </si>
   <si>
     <t>carreras ucasal</t>
   </si>
   <si>
-    <t>carreras ucasal a distancia</t>
-  </si>
-  <si>
-    <t>q carreras hay para estudiar</t>
-  </si>
-  <si>
-    <t>universidad siglo 21 salta</t>
-  </si>
-  <si>
     <t>licenciatura en comercio exterior y aduanas</t>
   </si>
   <si>
-    <t>gestion bancaria y financiera</t>
+    <t>universidades que dictan carreras a distancia</t>
+  </si>
+  <si>
+    <t>administracion universidades</t>
+  </si>
+  <si>
+    <t>upro san luis</t>
+  </si>
+  <si>
+    <t>administracion bancaria donde estudiar</t>
+  </si>
+  <si>
+    <t>administracion en una empresa</t>
+  </si>
+  <si>
+    <t>uces</t>
+  </si>
+  <si>
+    <t>universidades de administracion</t>
+  </si>
+  <si>
+    <t>ucasal learning</t>
+  </si>
+  <si>
+    <t>administración agropecuaria</t>
+  </si>
+  <si>
+    <t>administración de empresas neuquén</t>
   </si>
   <si>
     <t>universidad comodoro rivadavia</t>
   </si>
   <si>
+    <t>universidad seguridad informatica</t>
+  </si>
+  <si>
+    <t>carrera abogacía</t>
+  </si>
+  <si>
+    <t>universidad nacional de quilmes</t>
+  </si>
+  <si>
+    <t>carrera de abogado</t>
+  </si>
+  <si>
+    <t>carrera de administracion bancaria</t>
+  </si>
+  <si>
+    <t>universidad de economia</t>
+  </si>
+  <si>
+    <t>universidad nacional de salta</t>
+  </si>
+  <si>
+    <t>psicología a distancia</t>
+  </si>
+  <si>
     <t>ucasal abogacia</t>
   </si>
   <si>
-    <t>universidad nacional de salta</t>
-  </si>
-  <si>
-    <t>uces</t>
-  </si>
-  <si>
-    <t>universidad nacional de quilmes</t>
-  </si>
-  <si>
-    <t>upro san luis</t>
-  </si>
-  <si>
-    <t>ucasal learning</t>
-  </si>
-  <si>
-    <t>universidad de economia</t>
-  </si>
-  <si>
-    <t>universidades de administracion</t>
-  </si>
-  <si>
-    <t>universidades que dictan carreras a distancia</t>
-  </si>
-  <si>
-    <t>universidad seguridad informatica</t>
+    <t>licenciatura en administración</t>
+  </si>
+  <si>
+    <t>cursos gratis</t>
+  </si>
+  <si>
+    <t>cursos universidad</t>
+  </si>
+  <si>
+    <t>donde estudiar derecho</t>
+  </si>
+  <si>
+    <t>donde estudiar economia</t>
+  </si>
+  <si>
+    <t>licenciatura en educación a distancia</t>
+  </si>
+  <si>
+    <t>donde estudiar licenciatura en recursos humanos</t>
+  </si>
+  <si>
+    <t>donde estudiar traductorado de ingles</t>
+  </si>
+  <si>
+    <t>licenciatura en criminalística</t>
+  </si>
+  <si>
+    <t>economia carrera universitaria</t>
+  </si>
+  <si>
+    <t>licenciatura en análisis de datos</t>
+  </si>
+  <si>
+    <t>economia universidades</t>
+  </si>
+  <si>
+    <t>educación física a distancia</t>
+  </si>
+  <si>
+    <t>carrera de rrhh</t>
+  </si>
+  <si>
+    <t>licenciatura comercio internacional</t>
+  </si>
+  <si>
+    <t>escribanía a distancia</t>
+  </si>
+  <si>
+    <t>lic en rrhh</t>
+  </si>
+  <si>
+    <t>las relaciones internacionales</t>
+  </si>
+  <si>
+    <t>escribanía carrera</t>
+  </si>
+  <si>
+    <t>especialidad seguridad e higiene</t>
+  </si>
+  <si>
+    <t>higiene y seguridad</t>
+  </si>
+  <si>
+    <t>estudiar</t>
   </si>
   <si>
     <t>formación%20profesional%20online</t>
   </si>
   <si>
+    <t>estudiar guia de turismo</t>
+  </si>
+  <si>
+    <t>estudiar marketing y publicidad</t>
+  </si>
+  <si>
+    <t>cursos en línea</t>
+  </si>
+  <si>
+    <t>licenciatura en seguros a distancia</t>
+  </si>
+  <si>
+    <t>licenciatura marketing</t>
+  </si>
+  <si>
+    <t>licenciaturas</t>
+  </si>
+  <si>
     <t>trabajo social</t>
   </si>
   <si>
+    <t>tecnicatura programación a distancia</t>
+  </si>
+  <si>
+    <t>carrera educación física</t>
+  </si>
+  <si>
+    <t>carrera licenciatura en economia</t>
+  </si>
+  <si>
+    <t>carrera para bancario</t>
+  </si>
+  <si>
+    <t>carrera%20para%20secretaria</t>
+  </si>
+  <si>
+    <t>carreras</t>
+  </si>
+  <si>
     <t>carreras a distancia gratis</t>
   </si>
   <si>
-    <t>economia carrera universitaria</t>
-  </si>
-  <si>
-    <t>donde estudiar traductorado de ingles</t>
-  </si>
-  <si>
-    <t>donde estudiar licenciatura en recursos humanos</t>
-  </si>
-  <si>
-    <t>donde estudiar economia</t>
-  </si>
-  <si>
-    <t>donde estudiar derecho</t>
-  </si>
-  <si>
-    <t>cursos universidad</t>
-  </si>
-  <si>
-    <t>cursos gratis</t>
-  </si>
-  <si>
-    <t>cursos en línea</t>
+    <t>seguridad e higiene</t>
+  </si>
+  <si>
+    <t>relaciones publicas e institucionales</t>
+  </si>
+  <si>
+    <t>relaciones publicas a distancia</t>
+  </si>
+  <si>
+    <t>carreras cortas mendoza</t>
+  </si>
+  <si>
+    <t>recursos humanos a distancia</t>
+  </si>
+  <si>
+    <t>quiero estudiar economia</t>
+  </si>
+  <si>
+    <t>profesorado educación física</t>
+  </si>
+  <si>
+    <t>carreras universidad del comahue</t>
+  </si>
+  <si>
+    <t>pregrado</t>
+  </si>
+  <si>
+    <t>posgrado</t>
+  </si>
+  <si>
+    <t>catolica de salta</t>
+  </si>
+  <si>
+    <t>ceremonial y protocolo</t>
+  </si>
+  <si>
+    <t>medicina gratis argentina</t>
   </si>
   <si>
     <t>corredor inmobiliario</t>
   </si>
   <si>
-    <t>ceremonial y protocolo</t>
-  </si>
-  <si>
-    <t>catolica de salta</t>
-  </si>
-  <si>
-    <t>carreras universidad del comahue</t>
-  </si>
-  <si>
-    <t>carreras cortas mendoza</t>
-  </si>
-  <si>
-    <t>carreras</t>
-  </si>
-  <si>
-    <t>educación física a distancia</t>
-  </si>
-  <si>
-    <t>carrera%20para%20secretaria</t>
-  </si>
-  <si>
-    <t>carrera para bancario</t>
-  </si>
-  <si>
-    <t>carrera licenciatura en economia</t>
-  </si>
-  <si>
-    <t>carrera educación física</t>
-  </si>
-  <si>
-    <t>carrera de rrhh</t>
-  </si>
-  <si>
-    <t>carrera de administracion bancaria</t>
-  </si>
-  <si>
-    <t>carrera de abogado</t>
-  </si>
-  <si>
-    <t>carrera abogacía</t>
-  </si>
-  <si>
-    <t>administración de empresas neuquén</t>
-  </si>
-  <si>
-    <t>administración agropecuaria</t>
-  </si>
-  <si>
-    <t>administracion universidades</t>
-  </si>
-  <si>
-    <t>administracion en una empresa</t>
-  </si>
-  <si>
-    <t>administracion bancaria donde estudiar</t>
-  </si>
-  <si>
-    <t>economia universidades</t>
-  </si>
-  <si>
-    <t>escribanía a distancia</t>
-  </si>
-  <si>
-    <t>tecnicatura programación a distancia</t>
-  </si>
-  <si>
-    <t>licenciatura marketing</t>
-  </si>
-  <si>
-    <t>seguridad e higiene</t>
-  </si>
-  <si>
-    <t>relaciones publicas e institucionales</t>
-  </si>
-  <si>
-    <t>relaciones publicas a distancia</t>
-  </si>
-  <si>
-    <t>recursos humanos a distancia</t>
-  </si>
-  <si>
-    <t>quiero estudiar economia</t>
-  </si>
-  <si>
-    <t>psicología a distancia</t>
-  </si>
-  <si>
-    <t>psicologia</t>
-  </si>
-  <si>
-    <t>profesorado educación física</t>
-  </si>
-  <si>
-    <t>pregrado</t>
-  </si>
-  <si>
-    <t>posgrado</t>
-  </si>
-  <si>
-    <t>medicina gratis argentina</t>
-  </si>
-  <si>
     <t>marketing siglo 21</t>
-  </si>
-  <si>
-    <t>licenciaturas</t>
-  </si>
-  <si>
-    <t>licenciatura en higiene y seguridad</t>
-  </si>
-  <si>
-    <t>escribanía carrera</t>
-  </si>
-  <si>
-    <t>licenciatura en estudios internacionales</t>
-  </si>
-  <si>
-    <t>licenciatura en educación a distancia</t>
-  </si>
-  <si>
-    <t>licenciatura en criminalística</t>
-  </si>
-  <si>
-    <t>licenciatura en análisis de datos</t>
-  </si>
-  <si>
-    <t>licenciatura en administración</t>
-  </si>
-  <si>
-    <t>licenciatura comercio internacional</t>
-  </si>
-  <si>
-    <t>lic en rrhh</t>
-  </si>
-  <si>
-    <t>las relaciones internacionales</t>
-  </si>
-  <si>
-    <t>estudios bancarios</t>
-  </si>
-  <si>
-    <t>estudiar marketing y publicidad</t>
-  </si>
-  <si>
-    <t>estudiar guia de turismo</t>
-  </si>
-  <si>
-    <t>estudiar</t>
-  </si>
-  <si>
-    <t>especialidad seguridad e higiene</t>
   </si>
   <si>
     <t>carrera diseño grafico</t>
@@ -1723,7 +1732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1748,16 +1757,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>11363</v>
+        <v>11821</v>
       </c>
       <c r="C2">
-        <v>4715</v>
+        <v>5175</v>
       </c>
       <c r="D2">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E2">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1765,16 +1774,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>5861</v>
+        <v>6589</v>
       </c>
       <c r="C3">
-        <v>5999</v>
+        <v>6744</v>
       </c>
       <c r="D3">
-        <v>672</v>
+        <v>754</v>
       </c>
       <c r="E3">
-        <v>11.2</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1782,16 +1791,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>4846</v>
+        <v>4970</v>
       </c>
       <c r="C4">
-        <v>1065</v>
+        <v>1191</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1799,7 +1808,7 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>4260</v>
+        <v>4263</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1816,16 +1825,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>2621</v>
+        <v>3075</v>
       </c>
       <c r="C6">
-        <v>1964</v>
+        <v>2428</v>
       </c>
       <c r="D6">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="E6">
-        <v>7.94</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1833,16 +1842,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1504</v>
+        <v>1553</v>
       </c>
       <c r="C7">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>4.71</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1850,16 +1859,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>1450</v>
+        <v>1477</v>
       </c>
       <c r="C8">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8">
-        <v>3.7</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1867,16 +1876,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>1018</v>
+        <v>1056</v>
       </c>
       <c r="C9">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9">
-        <v>4.63</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1884,16 +1893,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>975</v>
+        <v>1009</v>
       </c>
       <c r="C10">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
       <c r="E10">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1901,16 +1910,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>914</v>
+        <v>959</v>
       </c>
       <c r="C11">
-        <v>434</v>
+        <v>480</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1918,16 +1927,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="C12">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1935,16 +1944,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>822</v>
+        <v>844</v>
       </c>
       <c r="C13">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1952,16 +1961,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>706</v>
+        <v>730</v>
       </c>
       <c r="C14">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="D14">
         <v>11</v>
       </c>
       <c r="E14">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1969,16 +1978,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1986,16 +1995,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="C16">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2003,16 +2012,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>635</v>
+        <v>648</v>
       </c>
       <c r="C17">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>3.43</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2020,16 +2029,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>587</v>
+        <v>624</v>
       </c>
       <c r="C18">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="D18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2037,16 +2046,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>581</v>
+        <v>611</v>
       </c>
       <c r="C19">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="D19">
         <v>9</v>
       </c>
       <c r="E19">
-        <v>3.98</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2054,16 +2063,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>555</v>
+        <v>581</v>
       </c>
       <c r="C20">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="D20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20">
-        <v>5.14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2071,16 +2080,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="C21">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21">
-        <v>5.66</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2088,16 +2097,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>517</v>
+        <v>546</v>
       </c>
       <c r="C22">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
       <c r="E22">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2105,16 +2114,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="C23">
-        <v>491</v>
+        <v>193</v>
       </c>
       <c r="D23">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>4.07</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2122,16 +2131,16 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C24">
-        <v>175</v>
+        <v>491</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E24">
-        <v>2.86</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2139,16 +2148,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="C25">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2156,16 +2165,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="C26">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>1.47</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2173,16 +2182,16 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="C27">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2190,16 +2199,16 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C28">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>5.95</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2207,16 +2216,16 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C29">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D29">
         <v>14</v>
       </c>
       <c r="E29">
-        <v>11.86</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2224,16 +2233,16 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="C30">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30">
-        <v>10.84</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2241,16 +2250,16 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C31">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="D31">
         <v>9</v>
       </c>
       <c r="E31">
-        <v>7.83</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2258,16 +2267,16 @@
         <v>35</v>
       </c>
       <c r="B32">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C32">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E32">
-        <v>11.01</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2275,16 +2284,16 @@
         <v>36</v>
       </c>
       <c r="B33">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C33">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2292,16 +2301,16 @@
         <v>37</v>
       </c>
       <c r="B34">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="C34">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2309,16 +2318,16 @@
         <v>38</v>
       </c>
       <c r="B35">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C35">
-        <v>59</v>
+        <v>185</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2326,16 +2335,16 @@
         <v>39</v>
       </c>
       <c r="B36">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C36">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2343,16 +2352,16 @@
         <v>40</v>
       </c>
       <c r="B37">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2360,16 +2369,16 @@
         <v>41</v>
       </c>
       <c r="B38">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D38">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2377,16 +2386,16 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C39">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E39">
-        <v>7.41</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2394,16 +2403,16 @@
         <v>43</v>
       </c>
       <c r="B40">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C40">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>2.7</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2411,16 +2420,16 @@
         <v>44</v>
       </c>
       <c r="B41">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C41">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41">
-        <v>8.890000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2519,10 +2528,10 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2530,16 +2539,16 @@
         <v>51</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
       <c r="E48">
-        <v>33.33</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2547,16 +2556,16 @@
         <v>52</v>
       </c>
       <c r="B49">
+        <v>4</v>
+      </c>
+      <c r="C49">
         <v>3</v>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2567,7 +2576,7 @@
         <v>3</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2598,10 +2607,10 @@
         <v>55</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2615,16 +2624,16 @@
         <v>56</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2632,10 +2641,10 @@
         <v>57</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2649,10 +2658,10 @@
         <v>58</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2666,10 +2675,10 @@
         <v>59</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2703,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2737,13 +2746,13 @@
         <v>1</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2788,7 +2797,7 @@
         <v>1</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2819,15 +2828,32 @@
         <v>68</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
         <v>100</v>
       </c>
     </row>
@@ -2843,7 +2869,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2860,24 +2886,24 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B2">
-        <v>46675</v>
+        <v>49110</v>
       </c>
       <c r="C2">
-        <v>20905</v>
+        <v>23384</v>
       </c>
       <c r="D2">
-        <v>1218</v>
+        <v>1377</v>
       </c>
       <c r="E2">
-        <v>5.83</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3">
         <v>228</v>
@@ -2894,7 +2920,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -2916,12 +2942,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E377"/>
+  <dimension ref="A1:E379"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2938,10 +2964,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B2">
-        <v>3004</v>
+        <v>3006</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2955,10 +2981,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3">
-        <v>2200</v>
+        <v>2204</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -2972,10 +2998,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2989,10 +3015,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3006,129 +3032,129 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6">
-        <v>1667</v>
+        <v>1868</v>
       </c>
       <c r="C6">
-        <v>1695</v>
+        <v>1898</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E6">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B7">
-        <v>790</v>
+        <v>820</v>
       </c>
       <c r="C7">
-        <v>279</v>
+        <v>413</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>3.58</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8">
-        <v>778</v>
+        <v>812</v>
       </c>
       <c r="C8">
-        <v>370</v>
+        <v>301</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>1.08</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9">
-        <v>769</v>
+        <v>807</v>
       </c>
       <c r="C9">
-        <v>298</v>
+        <v>809</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E9">
-        <v>3.02</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10">
-        <v>719</v>
+        <v>778</v>
       </c>
       <c r="C10">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="D10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10">
-        <v>3.36</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B11">
-        <v>715</v>
+        <v>750</v>
       </c>
       <c r="C11">
-        <v>712</v>
+        <v>358</v>
       </c>
       <c r="D11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11">
-        <v>1.97</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="C12">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12">
-        <v>3.61</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B13">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -3142,313 +3168,313 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B14">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="C14">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
       <c r="E14">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="C15">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
       <c r="E15">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="C16">
-        <v>202</v>
+        <v>517</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16">
-        <v>3.96</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B17">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B18">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="C18">
-        <v>482</v>
+        <v>288</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>1.66</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B19">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B20">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C20">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E20">
-        <v>0.76</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B21">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="C21">
-        <v>191</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>3.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B22">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="C22">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B23">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="C23">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
       <c r="E23">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="C24">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="D24">
         <v>5</v>
       </c>
       <c r="E24">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="C25">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>1.54</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26">
-        <v>359</v>
+        <v>394</v>
       </c>
       <c r="C26">
-        <v>143</v>
+        <v>366</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E26">
-        <v>4.2</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="C27">
-        <v>150</v>
+        <v>377</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>3.33</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B28">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="C28">
-        <v>347</v>
+        <v>196</v>
       </c>
       <c r="D28">
         <v>7</v>
       </c>
       <c r="E28">
-        <v>2.02</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B29">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="C29">
-        <v>321</v>
+        <v>160</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>1.25</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B30">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="C30">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>4.17</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B31">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C31">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E31">
-        <v>7.27</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B32">
         <v>322</v>
@@ -3465,7 +3491,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B33">
         <v>319</v>
@@ -3482,7 +3508,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B34">
         <v>309</v>
@@ -3499,591 +3525,591 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B35">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C35">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>2.14</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B36">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C36">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>1.89</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B38">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C38">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E38">
-        <v>8.789999999999999</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B39">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C39">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D39">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>12.28</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B40">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C40">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>3.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B41">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C41">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E41">
-        <v>1.25</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C42">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>7.35</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B43">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C43">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E43">
-        <v>8.039999999999999</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B44">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C44">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44">
-        <v>5.38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B45">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C45">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>1.28</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B46">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="C46">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D46">
         <v>7</v>
       </c>
       <c r="E46">
-        <v>6.48</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B47">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="C47">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D47">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E47">
-        <v>11.43</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B49">
         <v>211</v>
       </c>
       <c r="C49">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B50">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C50">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B51">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C51">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B52">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B53">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C53">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>3.17</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B54">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C54">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>1.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B55">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C55">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D55">
         <v>2</v>
       </c>
       <c r="E55">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B56">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C56">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>1.75</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B57">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B58">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C58">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="D58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E58">
-        <v>3.16</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B59">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C59">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>3.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B60">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B61">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C61">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>1.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B62">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B63">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C63">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E63">
-        <v>6.67</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B64">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C64">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>5.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B65">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C65">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B66">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C66">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>10</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67">
         <v>139</v>
       </c>
-      <c r="B67">
-        <v>132</v>
-      </c>
       <c r="C67">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B68">
         <v>132</v>
       </c>
       <c r="C68">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B69">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C69">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4094,24 +4120,24 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B70">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C70">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D70">
         <v>1</v>
       </c>
       <c r="E70">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B71">
         <v>122</v>
@@ -4128,10 +4154,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B72">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -4145,10 +4171,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B73">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C73">
         <v>2</v>
@@ -4162,13 +4188,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B74">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C74">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -4179,115 +4205,115 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B75">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C75">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E75">
-        <v>16</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B76">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B77">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C77">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D77">
         <v>6</v>
       </c>
       <c r="E77">
-        <v>12.5</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B78">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C78">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>4.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B79">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C79">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B80">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C80">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B81">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C81">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -4298,200 +4324,200 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B82">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B83">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C83">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E83">
-        <v>2.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B84">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B85">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C85">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="D85">
         <v>3</v>
       </c>
       <c r="E85">
-        <v>13.04</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B86">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C86">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>1.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B87">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B88">
         <v>78</v>
       </c>
       <c r="C88">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B89">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C89">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>6.25</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B90">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C90">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E90">
-        <v>2.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B91">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C91">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>2.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B92">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C92">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92">
-        <v>10</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B93">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C93">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -4502,7 +4528,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B94">
         <v>70</v>
@@ -4519,13 +4545,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B95">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -4536,13 +4562,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B96">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C96">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -4553,7 +4579,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B97">
         <v>64</v>
@@ -4570,47 +4596,47 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B98">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C98">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D98">
         <v>4</v>
       </c>
       <c r="E98">
-        <v>8.890000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B99">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C99">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D99">
         <v>3</v>
       </c>
       <c r="E99">
-        <v>5.77</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B100">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C100">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -4621,13 +4647,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B101">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C101">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -4638,7 +4664,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B102">
         <v>56</v>
@@ -4655,47 +4681,47 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B103">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C103">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B104">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C104">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B105">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -4706,13 +4732,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B106">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C106">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -4723,13 +4749,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B107">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C107">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -4740,13 +4766,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B108">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C108">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -4757,13 +4783,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B109">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C109">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -4774,13 +4800,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B110">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C110">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -4791,41 +4817,41 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B111">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C111">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B112">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C112">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D112">
         <v>4</v>
       </c>
       <c r="E112">
-        <v>8.890000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B113">
         <v>42</v>
@@ -4842,13 +4868,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B114">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -4859,30 +4885,30 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B115">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B116">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -4893,13 +4919,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B117">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C117">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -4910,13 +4936,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B118">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C118">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -4927,64 +4953,64 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B119">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C119">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E119">
-        <v>11.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B120">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C120">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E120">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B121">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C121">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121">
-        <v>3.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B122">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C122">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -4995,41 +5021,41 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B123">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C123">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B124">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C124">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B125">
         <v>35</v>
@@ -5046,7 +5072,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B126">
         <v>35</v>
@@ -5063,24 +5089,24 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B127">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B128">
         <v>32</v>
@@ -5097,58 +5123,58 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B129">
         <v>32</v>
       </c>
       <c r="C129">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B130">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C130">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>6.67</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B131">
         <v>29</v>
       </c>
       <c r="C131">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131">
-        <v>11.11</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B132">
         <v>27</v>
@@ -5165,7 +5191,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B133">
         <v>27</v>
@@ -5182,7 +5208,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B134">
         <v>27</v>
@@ -5199,13 +5225,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B135">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C135">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -5216,13 +5242,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B136">
         <v>26</v>
       </c>
       <c r="C136">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -5233,13 +5259,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B137">
         <v>26</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -5250,7 +5276,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B138">
         <v>25</v>
@@ -5267,7 +5293,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B139">
         <v>25</v>
@@ -5284,41 +5310,41 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B140">
         <v>24</v>
       </c>
       <c r="C140">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B141">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C141">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B142">
         <v>23</v>
@@ -5335,24 +5361,24 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B143">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C143">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D143">
         <v>1</v>
       </c>
       <c r="E143">
-        <v>4.55</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B144">
         <v>22</v>
@@ -5369,13 +5395,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B145">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -5386,13 +5412,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B146">
         <v>20</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -5403,30 +5429,30 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B147">
         <v>20</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B148">
         <v>20</v>
       </c>
       <c r="C148">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -5437,30 +5463,30 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B149">
         <v>20</v>
       </c>
       <c r="C149">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B150">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C150">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -5471,7 +5497,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B151">
         <v>19</v>
@@ -5488,7 +5514,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B152">
         <v>19</v>
@@ -5505,13 +5531,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B153">
         <v>19</v>
       </c>
       <c r="C153">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -5522,13 +5548,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B154">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -5539,13 +5565,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B155">
         <v>18</v>
       </c>
       <c r="C155">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -5556,13 +5582,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B156">
         <v>18</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -5573,47 +5599,47 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B157">
         <v>18</v>
       </c>
       <c r="C157">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B158">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C158">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B159">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C159">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -5624,13 +5650,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B160">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C160">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D160">
         <v>0</v>
@@ -5641,13 +5667,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B161">
         <v>17</v>
       </c>
       <c r="C161">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D161">
         <v>0</v>
@@ -5658,30 +5684,30 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B162">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C162">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B163">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C163">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -5692,13 +5718,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B164">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C164">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -5709,13 +5735,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B165">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C165">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -5726,13 +5752,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B166">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C166">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -5743,13 +5769,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B167">
         <v>15</v>
       </c>
       <c r="C167">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -5760,7 +5786,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B168">
         <v>15</v>
@@ -5777,7 +5803,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B169">
         <v>15</v>
@@ -5794,7 +5820,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B170">
         <v>15</v>
@@ -5811,13 +5837,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B171">
         <v>15</v>
       </c>
       <c r="C171">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -5828,13 +5854,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B172">
         <v>14</v>
       </c>
       <c r="C172">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D172">
         <v>0</v>
@@ -5845,13 +5871,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B173">
         <v>14</v>
       </c>
       <c r="C173">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -5862,13 +5888,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B174">
         <v>14</v>
       </c>
       <c r="C174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -5879,30 +5905,30 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B175">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C175">
         <v>14</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B176">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -5913,13 +5939,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B177">
         <v>13</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -5930,7 +5956,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B178">
         <v>13</v>
@@ -5947,13 +5973,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B179">
         <v>13</v>
       </c>
       <c r="C179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -5964,13 +5990,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B180">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C180">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -5981,7 +6007,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B181">
         <v>12</v>
@@ -5990,24 +6016,24 @@
         <v>12</v>
       </c>
       <c r="D181">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E181">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B182">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C182">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182">
         <v>16.67</v>
@@ -6015,24 +6041,24 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B183">
         <v>11</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B184">
         <v>11</v>
@@ -6049,13 +6075,13 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B185">
         <v>11</v>
       </c>
       <c r="C185">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -6066,13 +6092,13 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B186">
         <v>11</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -6083,13 +6109,13 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B187">
         <v>11</v>
       </c>
       <c r="C187">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -6100,13 +6126,13 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B188">
         <v>10</v>
       </c>
       <c r="C188">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -6117,7 +6143,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B189">
         <v>10</v>
@@ -6134,13 +6160,13 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B190">
         <v>10</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -6151,7 +6177,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B191">
         <v>10</v>
@@ -6168,7 +6194,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B192">
         <v>10</v>
@@ -6185,7 +6211,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B193">
         <v>10</v>
@@ -6202,13 +6228,13 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B194">
         <v>10</v>
       </c>
       <c r="C194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -6219,13 +6245,13 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B195">
         <v>10</v>
       </c>
       <c r="C195">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -6236,13 +6262,13 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B196">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D196">
         <v>0</v>
@@ -6253,13 +6279,13 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B197">
         <v>9</v>
       </c>
       <c r="C197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -6270,7 +6296,7 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B198">
         <v>9</v>
@@ -6287,7 +6313,7 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B199">
         <v>9</v>
@@ -6304,13 +6330,13 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B200">
         <v>9</v>
       </c>
       <c r="C200">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D200">
         <v>0</v>
@@ -6321,7 +6347,7 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B201">
         <v>9</v>
@@ -6338,7 +6364,7 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B202">
         <v>9</v>
@@ -6355,13 +6381,13 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B203">
         <v>9</v>
       </c>
       <c r="C203">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -6372,13 +6398,13 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B204">
         <v>9</v>
       </c>
       <c r="C204">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -6389,41 +6415,41 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B205">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C205">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E205">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B206">
         <v>8</v>
       </c>
       <c r="C206">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D206">
         <v>1</v>
       </c>
       <c r="E206">
-        <v>25</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B207">
         <v>8</v>
@@ -6440,13 +6466,13 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B208">
         <v>8</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -6457,13 +6483,13 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B209">
         <v>8</v>
       </c>
       <c r="C209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -6474,7 +6500,7 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B210">
         <v>8</v>
@@ -6491,30 +6517,30 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B211">
         <v>8</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E211">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B212">
         <v>8</v>
       </c>
       <c r="C212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -6525,13 +6551,13 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B213">
         <v>7</v>
       </c>
       <c r="C213">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -6542,13 +6568,13 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B214">
         <v>7</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -6559,13 +6585,13 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B215">
         <v>7</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -6576,7 +6602,7 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B216">
         <v>7</v>
@@ -6593,13 +6619,13 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B217">
         <v>7</v>
       </c>
       <c r="C217">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -6610,7 +6636,7 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B218">
         <v>7</v>
@@ -6627,13 +6653,13 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B219">
         <v>7</v>
       </c>
       <c r="C219">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -6644,13 +6670,13 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B220">
         <v>7</v>
       </c>
       <c r="C220">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D220">
         <v>0</v>
@@ -6661,7 +6687,7 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B221">
         <v>7</v>
@@ -6678,13 +6704,13 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B222">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C222">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -6695,7 +6721,7 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B223">
         <v>6</v>
@@ -6712,13 +6738,13 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B224">
         <v>6</v>
       </c>
       <c r="C224">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D224">
         <v>0</v>
@@ -6729,13 +6755,13 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B225">
         <v>6</v>
       </c>
       <c r="C225">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D225">
         <v>0</v>
@@ -6746,24 +6772,24 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B226">
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E226">
-        <v>0</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B227">
         <v>6</v>
@@ -6780,30 +6806,30 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B228">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C228">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E228">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B229">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -6814,13 +6840,13 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B230">
         <v>5</v>
       </c>
       <c r="C230">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -6831,30 +6857,30 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B231">
         <v>5</v>
       </c>
       <c r="C231">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E231">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B232">
         <v>5</v>
       </c>
       <c r="C232">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D232">
         <v>0</v>
@@ -6865,13 +6891,13 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B233">
         <v>5</v>
       </c>
       <c r="C233">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D233">
         <v>0</v>
@@ -6882,13 +6908,13 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B234">
         <v>5</v>
       </c>
       <c r="C234">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D234">
         <v>0</v>
@@ -6899,7 +6925,7 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B235">
         <v>5</v>
@@ -6916,30 +6942,30 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B236">
         <v>5</v>
       </c>
       <c r="C236">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E236">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B237">
         <v>5</v>
       </c>
       <c r="C237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D237">
         <v>0</v>
@@ -6950,13 +6976,13 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B238">
         <v>5</v>
       </c>
       <c r="C238">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D238">
         <v>0</v>
@@ -6967,7 +6993,7 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B239">
         <v>5</v>
@@ -6984,30 +7010,30 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B240">
         <v>5</v>
       </c>
       <c r="C240">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E240">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B241">
         <v>5</v>
       </c>
       <c r="C241">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D241">
         <v>0</v>
@@ -7018,7 +7044,7 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B242">
         <v>5</v>
@@ -7035,13 +7061,13 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B243">
         <v>5</v>
       </c>
       <c r="C243">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D243">
         <v>0</v>
@@ -7052,13 +7078,13 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B244">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C244">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D244">
         <v>0</v>
@@ -7069,13 +7095,13 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B245">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D245">
         <v>0</v>
@@ -7086,10 +7112,10 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -7103,7 +7129,7 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B247">
         <v>4</v>
@@ -7120,13 +7146,13 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B248">
         <v>4</v>
       </c>
       <c r="C248">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D248">
         <v>0</v>
@@ -7137,13 +7163,13 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B249">
         <v>4</v>
       </c>
       <c r="C249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D249">
         <v>0</v>
@@ -7154,13 +7180,13 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B250">
         <v>4</v>
       </c>
       <c r="C250">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D250">
         <v>0</v>
@@ -7171,7 +7197,7 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B251">
         <v>4</v>
@@ -7188,30 +7214,30 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B252">
         <v>4</v>
       </c>
       <c r="C252">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E252">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:5">
       <c r="A253" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B253">
         <v>4</v>
       </c>
       <c r="C253">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D253">
         <v>0</v>
@@ -7222,13 +7248,13 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B254">
         <v>4</v>
       </c>
       <c r="C254">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D254">
         <v>0</v>
@@ -7239,13 +7265,13 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B255">
         <v>4</v>
       </c>
       <c r="C255">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D255">
         <v>0</v>
@@ -7256,7 +7282,7 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B256">
         <v>4</v>
@@ -7273,13 +7299,13 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B257">
         <v>4</v>
       </c>
       <c r="C257">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D257">
         <v>0</v>
@@ -7290,13 +7316,13 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B258">
+        <v>4</v>
+      </c>
+      <c r="C258">
         <v>3</v>
-      </c>
-      <c r="C258">
-        <v>0</v>
       </c>
       <c r="D258">
         <v>0</v>
@@ -7307,10 +7333,10 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B259">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -7324,13 +7350,13 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B260">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C260">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D260">
         <v>0</v>
@@ -7341,10 +7367,10 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B261">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -7358,13 +7384,13 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B262">
         <v>3</v>
       </c>
       <c r="C262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D262">
         <v>0</v>
@@ -7375,13 +7401,13 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B263">
         <v>3</v>
       </c>
       <c r="C263">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D263">
         <v>0</v>
@@ -7392,13 +7418,13 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B264">
         <v>3</v>
       </c>
       <c r="C264">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D264">
         <v>0</v>
@@ -7409,30 +7435,30 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B265">
         <v>3</v>
       </c>
       <c r="C265">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E265">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B266">
         <v>3</v>
       </c>
       <c r="C266">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D266">
         <v>0</v>
@@ -7443,13 +7469,13 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B267">
         <v>3</v>
       </c>
       <c r="C267">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D267">
         <v>0</v>
@@ -7460,13 +7486,13 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B268">
         <v>3</v>
       </c>
       <c r="C268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D268">
         <v>0</v>
@@ -7477,13 +7503,13 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B269">
         <v>3</v>
       </c>
       <c r="C269">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D269">
         <v>0</v>
@@ -7494,13 +7520,13 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B270">
         <v>3</v>
       </c>
       <c r="C270">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D270">
         <v>0</v>
@@ -7511,13 +7537,13 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B271">
         <v>3</v>
       </c>
       <c r="C271">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D271">
         <v>0</v>
@@ -7528,13 +7554,13 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B272">
         <v>3</v>
       </c>
       <c r="C272">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D272">
         <v>0</v>
@@ -7545,13 +7571,13 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B273">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D273">
         <v>0</v>
@@ -7562,10 +7588,10 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -7579,10 +7605,10 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B275">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C275">
         <v>0</v>
@@ -7596,13 +7622,13 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B276">
         <v>2</v>
       </c>
       <c r="C276">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D276">
         <v>0</v>
@@ -7613,13 +7639,13 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B277">
         <v>2</v>
       </c>
       <c r="C277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D277">
         <v>0</v>
@@ -7630,7 +7656,7 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B278">
         <v>2</v>
@@ -7647,30 +7673,30 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B279">
         <v>2</v>
       </c>
       <c r="C279">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D279">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E279">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:5">
       <c r="A280" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B280">
         <v>2</v>
       </c>
       <c r="C280">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D280">
         <v>0</v>
@@ -7681,13 +7707,13 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B281">
         <v>2</v>
       </c>
       <c r="C281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D281">
         <v>0</v>
@@ -7698,7 +7724,7 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B282">
         <v>2</v>
@@ -7715,13 +7741,13 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B283">
         <v>2</v>
       </c>
       <c r="C283">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D283">
         <v>0</v>
@@ -7732,13 +7758,13 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B284">
         <v>2</v>
       </c>
       <c r="C284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D284">
         <v>0</v>
@@ -7749,13 +7775,13 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B285">
         <v>2</v>
       </c>
       <c r="C285">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D285">
         <v>0</v>
@@ -7766,13 +7792,13 @@
     </row>
     <row r="286" spans="1:5">
       <c r="A286" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B286">
         <v>2</v>
       </c>
       <c r="C286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D286">
         <v>0</v>
@@ -7783,7 +7809,7 @@
     </row>
     <row r="287" spans="1:5">
       <c r="A287" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B287">
         <v>2</v>
@@ -7800,7 +7826,7 @@
     </row>
     <row r="288" spans="1:5">
       <c r="A288" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B288">
         <v>2</v>
@@ -7817,7 +7843,7 @@
     </row>
     <row r="289" spans="1:5">
       <c r="A289" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B289">
         <v>2</v>
@@ -7834,13 +7860,13 @@
     </row>
     <row r="290" spans="1:5">
       <c r="A290" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B290">
         <v>2</v>
       </c>
       <c r="C290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D290">
         <v>0</v>
@@ -7851,13 +7877,13 @@
     </row>
     <row r="291" spans="1:5">
       <c r="A291" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B291">
         <v>2</v>
       </c>
       <c r="C291">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D291">
         <v>0</v>
@@ -7868,13 +7894,13 @@
     </row>
     <row r="292" spans="1:5">
       <c r="A292" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B292">
         <v>2</v>
       </c>
       <c r="C292">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D292">
         <v>0</v>
@@ -7885,7 +7911,7 @@
     </row>
     <row r="293" spans="1:5">
       <c r="A293" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B293">
         <v>2</v>
@@ -7902,13 +7928,13 @@
     </row>
     <row r="294" spans="1:5">
       <c r="A294" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B294">
         <v>2</v>
       </c>
       <c r="C294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D294">
         <v>0</v>
@@ -7919,13 +7945,13 @@
     </row>
     <row r="295" spans="1:5">
       <c r="A295" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B295">
         <v>2</v>
       </c>
       <c r="C295">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D295">
         <v>0</v>
@@ -7936,24 +7962,24 @@
     </row>
     <row r="296" spans="1:5">
       <c r="A296" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B296">
         <v>2</v>
       </c>
       <c r="C296">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D296">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E296">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="297" spans="1:5">
       <c r="A297" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B297">
         <v>2</v>
@@ -7970,7 +7996,7 @@
     </row>
     <row r="298" spans="1:5">
       <c r="A298" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B298">
         <v>2</v>
@@ -7987,7 +8013,7 @@
     </row>
     <row r="299" spans="1:5">
       <c r="A299" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B299">
         <v>2</v>
@@ -8004,7 +8030,7 @@
     </row>
     <row r="300" spans="1:5">
       <c r="A300" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B300">
         <v>2</v>
@@ -8021,7 +8047,7 @@
     </row>
     <row r="301" spans="1:5">
       <c r="A301" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B301">
         <v>2</v>
@@ -8038,7 +8064,7 @@
     </row>
     <row r="302" spans="1:5">
       <c r="A302" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B302">
         <v>2</v>
@@ -8055,10 +8081,10 @@
     </row>
     <row r="303" spans="1:5">
       <c r="A303" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -8072,10 +8098,10 @@
     </row>
     <row r="304" spans="1:5">
       <c r="A304" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B304">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -8089,10 +8115,10 @@
     </row>
     <row r="305" spans="1:5">
       <c r="A305" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B305">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -8106,13 +8132,13 @@
     </row>
     <row r="306" spans="1:5">
       <c r="A306" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B306">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C306">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D306">
         <v>0</v>
@@ -8123,7 +8149,7 @@
     </row>
     <row r="307" spans="1:5">
       <c r="A307" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B307">
         <v>1</v>
@@ -8140,13 +8166,13 @@
     </row>
     <row r="308" spans="1:5">
       <c r="A308" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B308">
         <v>1</v>
       </c>
       <c r="C308">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D308">
         <v>0</v>
@@ -8157,7 +8183,7 @@
     </row>
     <row r="309" spans="1:5">
       <c r="A309" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B309">
         <v>1</v>
@@ -8174,13 +8200,13 @@
     </row>
     <row r="310" spans="1:5">
       <c r="A310" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B310">
         <v>1</v>
       </c>
       <c r="C310">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D310">
         <v>0</v>
@@ -8191,13 +8217,13 @@
     </row>
     <row r="311" spans="1:5">
       <c r="A311" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B311">
         <v>1</v>
       </c>
       <c r="C311">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D311">
         <v>0</v>
@@ -8208,7 +8234,7 @@
     </row>
     <row r="312" spans="1:5">
       <c r="A312" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B312">
         <v>1</v>
@@ -8225,7 +8251,7 @@
     </row>
     <row r="313" spans="1:5">
       <c r="A313" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B313">
         <v>1</v>
@@ -8242,13 +8268,13 @@
     </row>
     <row r="314" spans="1:5">
       <c r="A314" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B314">
         <v>1</v>
       </c>
       <c r="C314">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D314">
         <v>0</v>
@@ -8259,7 +8285,7 @@
     </row>
     <row r="315" spans="1:5">
       <c r="A315" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B315">
         <v>1</v>
@@ -8276,7 +8302,7 @@
     </row>
     <row r="316" spans="1:5">
       <c r="A316" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B316">
         <v>1</v>
@@ -8293,13 +8319,13 @@
     </row>
     <row r="317" spans="1:5">
       <c r="A317" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B317">
         <v>1</v>
       </c>
       <c r="C317">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -8310,7 +8336,7 @@
     </row>
     <row r="318" spans="1:5">
       <c r="A318" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B318">
         <v>1</v>
@@ -8327,7 +8353,7 @@
     </row>
     <row r="319" spans="1:5">
       <c r="A319" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B319">
         <v>1</v>
@@ -8344,13 +8370,13 @@
     </row>
     <row r="320" spans="1:5">
       <c r="A320" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B320">
         <v>1</v>
       </c>
       <c r="C320">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D320">
         <v>0</v>
@@ -8361,13 +8387,13 @@
     </row>
     <row r="321" spans="1:5">
       <c r="A321" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B321">
         <v>1</v>
       </c>
       <c r="C321">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D321">
         <v>0</v>
@@ -8378,7 +8404,7 @@
     </row>
     <row r="322" spans="1:5">
       <c r="A322" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B322">
         <v>1</v>
@@ -8395,7 +8421,7 @@
     </row>
     <row r="323" spans="1:5">
       <c r="A323" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B323">
         <v>1</v>
@@ -8412,7 +8438,7 @@
     </row>
     <row r="324" spans="1:5">
       <c r="A324" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B324">
         <v>1</v>
@@ -8429,7 +8455,7 @@
     </row>
     <row r="325" spans="1:5">
       <c r="A325" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B325">
         <v>1</v>
@@ -8446,7 +8472,7 @@
     </row>
     <row r="326" spans="1:5">
       <c r="A326" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B326">
         <v>1</v>
@@ -8463,7 +8489,7 @@
     </row>
     <row r="327" spans="1:5">
       <c r="A327" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B327">
         <v>1</v>
@@ -8480,7 +8506,7 @@
     </row>
     <row r="328" spans="1:5">
       <c r="A328" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B328">
         <v>1</v>
@@ -8497,7 +8523,7 @@
     </row>
     <row r="329" spans="1:5">
       <c r="A329" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B329">
         <v>1</v>
@@ -8514,13 +8540,13 @@
     </row>
     <row r="330" spans="1:5">
       <c r="A330" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B330">
         <v>1</v>
       </c>
       <c r="C330">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D330">
         <v>0</v>
@@ -8531,13 +8557,13 @@
     </row>
     <row r="331" spans="1:5">
       <c r="A331" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B331">
         <v>1</v>
       </c>
       <c r="C331">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D331">
         <v>0</v>
@@ -8548,7 +8574,7 @@
     </row>
     <row r="332" spans="1:5">
       <c r="A332" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B332">
         <v>1</v>
@@ -8565,7 +8591,7 @@
     </row>
     <row r="333" spans="1:5">
       <c r="A333" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B333">
         <v>1</v>
@@ -8582,13 +8608,13 @@
     </row>
     <row r="334" spans="1:5">
       <c r="A334" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B334">
         <v>1</v>
       </c>
       <c r="C334">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D334">
         <v>0</v>
@@ -8599,7 +8625,7 @@
     </row>
     <row r="335" spans="1:5">
       <c r="A335" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B335">
         <v>1</v>
@@ -8616,7 +8642,7 @@
     </row>
     <row r="336" spans="1:5">
       <c r="A336" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B336">
         <v>1</v>
@@ -8633,7 +8659,7 @@
     </row>
     <row r="337" spans="1:5">
       <c r="A337" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B337">
         <v>1</v>
@@ -8650,7 +8676,7 @@
     </row>
     <row r="338" spans="1:5">
       <c r="A338" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B338">
         <v>1</v>
@@ -8667,7 +8693,7 @@
     </row>
     <row r="339" spans="1:5">
       <c r="A339" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B339">
         <v>1</v>
@@ -8684,13 +8710,13 @@
     </row>
     <row r="340" spans="1:5">
       <c r="A340" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B340">
         <v>1</v>
       </c>
       <c r="C340">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D340">
         <v>0</v>
@@ -8701,7 +8727,7 @@
     </row>
     <row r="341" spans="1:5">
       <c r="A341" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B341">
         <v>1</v>
@@ -8718,13 +8744,13 @@
     </row>
     <row r="342" spans="1:5">
       <c r="A342" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B342">
         <v>1</v>
       </c>
       <c r="C342">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D342">
         <v>0</v>
@@ -8735,7 +8761,7 @@
     </row>
     <row r="343" spans="1:5">
       <c r="A343" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B343">
         <v>1</v>
@@ -8752,13 +8778,13 @@
     </row>
     <row r="344" spans="1:5">
       <c r="A344" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B344">
         <v>1</v>
       </c>
       <c r="C344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D344">
         <v>0</v>
@@ -8769,7 +8795,7 @@
     </row>
     <row r="345" spans="1:5">
       <c r="A345" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B345">
         <v>1</v>
@@ -8786,7 +8812,7 @@
     </row>
     <row r="346" spans="1:5">
       <c r="A346" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B346">
         <v>1</v>
@@ -8803,13 +8829,13 @@
     </row>
     <row r="347" spans="1:5">
       <c r="A347" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B347">
         <v>1</v>
       </c>
       <c r="C347">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D347">
         <v>0</v>
@@ -8820,13 +8846,13 @@
     </row>
     <row r="348" spans="1:5">
       <c r="A348" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B348">
         <v>1</v>
       </c>
       <c r="C348">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D348">
         <v>0</v>
@@ -8837,13 +8863,13 @@
     </row>
     <row r="349" spans="1:5">
       <c r="A349" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B349">
         <v>1</v>
       </c>
       <c r="C349">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D349">
         <v>0</v>
@@ -8854,7 +8880,7 @@
     </row>
     <row r="350" spans="1:5">
       <c r="A350" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B350">
         <v>1</v>
@@ -8871,7 +8897,7 @@
     </row>
     <row r="351" spans="1:5">
       <c r="A351" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B351">
         <v>1</v>
@@ -8888,7 +8914,7 @@
     </row>
     <row r="352" spans="1:5">
       <c r="A352" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B352">
         <v>1</v>
@@ -8905,13 +8931,13 @@
     </row>
     <row r="353" spans="1:5">
       <c r="A353" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B353">
         <v>1</v>
       </c>
       <c r="C353">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D353">
         <v>0</v>
@@ -8922,13 +8948,13 @@
     </row>
     <row r="354" spans="1:5">
       <c r="A354" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B354">
         <v>1</v>
       </c>
       <c r="C354">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D354">
         <v>0</v>
@@ -8939,24 +8965,24 @@
     </row>
     <row r="355" spans="1:5">
       <c r="A355" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B355">
         <v>1</v>
       </c>
       <c r="C355">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D355">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E355">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:5">
       <c r="A356" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B356">
         <v>1</v>
@@ -8973,7 +8999,7 @@
     </row>
     <row r="357" spans="1:5">
       <c r="A357" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B357">
         <v>1</v>
@@ -8990,7 +9016,7 @@
     </row>
     <row r="358" spans="1:5">
       <c r="A358" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B358">
         <v>1</v>
@@ -9007,7 +9033,7 @@
     </row>
     <row r="359" spans="1:5">
       <c r="A359" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B359">
         <v>1</v>
@@ -9024,7 +9050,7 @@
     </row>
     <row r="360" spans="1:5">
       <c r="A360" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B360">
         <v>1</v>
@@ -9041,7 +9067,7 @@
     </row>
     <row r="361" spans="1:5">
       <c r="A361" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B361">
         <v>1</v>
@@ -9058,13 +9084,13 @@
     </row>
     <row r="362" spans="1:5">
       <c r="A362" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B362">
         <v>1</v>
       </c>
       <c r="C362">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D362">
         <v>0</v>
@@ -9075,7 +9101,7 @@
     </row>
     <row r="363" spans="1:5">
       <c r="A363" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B363">
         <v>1</v>
@@ -9092,7 +9118,7 @@
     </row>
     <row r="364" spans="1:5">
       <c r="A364" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B364">
         <v>1</v>
@@ -9109,7 +9135,7 @@
     </row>
     <row r="365" spans="1:5">
       <c r="A365" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B365">
         <v>1</v>
@@ -9126,13 +9152,13 @@
     </row>
     <row r="366" spans="1:5">
       <c r="A366" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B366">
         <v>1</v>
       </c>
       <c r="C366">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D366">
         <v>0</v>
@@ -9143,7 +9169,7 @@
     </row>
     <row r="367" spans="1:5">
       <c r="A367" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B367">
         <v>1</v>
@@ -9160,7 +9186,7 @@
     </row>
     <row r="368" spans="1:5">
       <c r="A368" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B368">
         <v>1</v>
@@ -9177,7 +9203,7 @@
     </row>
     <row r="369" spans="1:5">
       <c r="A369" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B369">
         <v>1</v>
@@ -9194,7 +9220,7 @@
     </row>
     <row r="370" spans="1:5">
       <c r="A370" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B370">
         <v>1</v>
@@ -9211,7 +9237,7 @@
     </row>
     <row r="371" spans="1:5">
       <c r="A371" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B371">
         <v>1</v>
@@ -9228,13 +9254,13 @@
     </row>
     <row r="372" spans="1:5">
       <c r="A372" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B372">
         <v>1</v>
       </c>
       <c r="C372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D372">
         <v>0</v>
@@ -9245,13 +9271,13 @@
     </row>
     <row r="373" spans="1:5">
       <c r="A373" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B373">
         <v>1</v>
       </c>
       <c r="C373">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D373">
         <v>0</v>
@@ -9262,7 +9288,7 @@
     </row>
     <row r="374" spans="1:5">
       <c r="A374" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B374">
         <v>1</v>
@@ -9279,7 +9305,7 @@
     </row>
     <row r="375" spans="1:5">
       <c r="A375" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B375">
         <v>1</v>
@@ -9296,7 +9322,7 @@
     </row>
     <row r="376" spans="1:5">
       <c r="A376" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B376">
         <v>1</v>
@@ -9313,18 +9339,52 @@
     </row>
     <row r="377" spans="1:5">
       <c r="A377" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B377">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C377">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D377">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" t="s">
+        <v>451</v>
+      </c>
+      <c r="B378">
+        <v>1</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" t="s">
+        <v>452</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>1</v>
+      </c>
+      <c r="D379">
+        <v>1</v>
+      </c>
+      <c r="E379">
         <v>100</v>
       </c>
     </row>

--- a/marketing_report/outputs/Grado_Pregrado/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
@@ -1757,7 +1757,7 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>11821</v>
+        <v>11822</v>
       </c>
       <c r="C2">
         <v>5175</v>
@@ -1774,16 +1774,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>6589</v>
+        <v>6590</v>
       </c>
       <c r="C3">
-        <v>6744</v>
+        <v>6745</v>
       </c>
       <c r="D3">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E3">
-        <v>11.18</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1808,7 +1808,7 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>4263</v>
+        <v>4262</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -2889,16 +2889,16 @@
         <v>71</v>
       </c>
       <c r="B2">
-        <v>49110</v>
+        <v>49111</v>
       </c>
       <c r="C2">
-        <v>23384</v>
+        <v>23385</v>
       </c>
       <c r="D2">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="E2">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2967,7 +2967,7 @@
         <v>75</v>
       </c>
       <c r="B2">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -3035,7 +3035,7 @@
         <v>79</v>
       </c>
       <c r="B6">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="C6">
         <v>1898</v>
